--- a/output/pdf_financials_xlsx/ERA.xlsx
+++ b/output/pdf_financials_xlsx/ERA.xlsx
@@ -6092,31 +6092,31 @@
         <v>0</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.455096</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.532531</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.927516</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.927516</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.872789</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.872789</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.55764</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.398877</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>4.45176</v>
       </c>
     </row>
     <row r="93">
@@ -10614,7 +10614,11 @@
           <t>Share-based payment reserve (note 21)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -11945,7 +11949,11 @@
           <t>Share-based payment reserve (note 19)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -12307,7 +12315,11 @@
           <t>Share based payment reserve (note 20)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -15525,7 +15537,11 @@
           <t>Share based payment reserve (note 18)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -16524,7 +16540,11 @@
           <t>Share based payment reserve (note 17)</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -16611,7 +16631,11 @@
           <t>Foreign currency translation reserve (note 17)</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ERA.xlsx
+++ b/output/pdf_financials_xlsx/ERA.xlsx
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001254</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003918</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00033</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -2137,13 +2137,13 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.29807</v>
+        <v>-2.296816</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.758714</v>
+        <v>-1.754796</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-9.763612</v>
+        <v>-9.763282</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-1.138192</v>
@@ -2269,13 +2269,13 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.29807</v>
+        <v>-2.296816</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.758714</v>
+        <v>-1.754796</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-9.763612</v>
+        <v>-9.763282</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-1.138192</v>
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.237038</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -2568,31 +2568,31 @@
         <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.351808</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.952375</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.579361</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.033192</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.290427</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.30913</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.015212</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.014599</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.206637</v>
       </c>
     </row>
     <row r="35">
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.237038</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -2688,31 +2688,31 @@
         <v>0</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.043357</v>
+        <v>1.395165</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.044367</v>
+        <v>0.996742</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.010161</v>
+        <v>0.589522</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.033192</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.290427</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.30913</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.015212</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.014599</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.206637</v>
       </c>
     </row>
     <row r="37">
@@ -3408,31 +3408,31 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.476147</v>
+        <v>0.124339</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.96994</v>
+        <v>0.017565</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.590631</v>
+        <v>0.01127</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.034</v>
+        <v>0.000808</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.295586</v>
+        <v>0.005159</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.38477</v>
+        <v>0.07564</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.041176</v>
+        <v>0.025964</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.030216</v>
+        <v>0.015617</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.211927</v>
+        <v>0.00529</v>
       </c>
     </row>
     <row r="49">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -45833,7 +45833,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -48171,7 +48171,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -50337,7 +50337,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -54592,7 +54592,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -54687,7 +54687,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -57407,7 +57407,7 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -57500,7 +57500,7 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">

--- a/output/pdf_financials_xlsx/ERA.xlsx
+++ b/output/pdf_financials_xlsx/ERA.xlsx
@@ -7321,7 +7321,7 @@
         <v>0</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="113">
@@ -22618,7 +22618,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ERA.xlsx
+++ b/output/pdf_financials_xlsx/ERA.xlsx
@@ -623,10 +623,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
@@ -755,10 +753,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
@@ -821,10 +817,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
@@ -887,10 +881,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
@@ -953,10 +945,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
@@ -1085,10 +1075,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -1151,10 +1139,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
@@ -1217,10 +1203,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
@@ -1283,10 +1267,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
@@ -1349,10 +1331,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C16" s="3" t="n">
+        <v>-0.066979</v>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
@@ -1415,10 +1395,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
@@ -1645,10 +1623,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C20" s="3" t="n">
+        <v>-0.066979</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
@@ -1711,10 +1687,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
@@ -1777,10 +1751,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
@@ -1843,10 +1815,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C23" s="3" t="n">
+        <v>-0.066979</v>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
@@ -1907,10 +1877,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C24" s="3" t="n">
+        <v>-0.04</v>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
@@ -1973,10 +1941,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C25" s="3" t="n">
+        <v>-0.04</v>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
@@ -2039,10 +2005,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C26" s="3" t="n">
+        <v>1.674475</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -2111,10 +2075,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C27" s="3" t="n">
+        <v>-0.066979</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -2177,10 +2139,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
@@ -2243,10 +2203,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C29" s="3" t="n">
+        <v>-0.066979</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -2391,10 +2349,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
@@ -2940,7 +2896,7 @@
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.014632</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>0</v>
@@ -3000,7 +2956,7 @@
         <v>0.002413</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.015774</v>
+        <v>0.030406</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>0.005934</v>
@@ -3420,7 +3376,7 @@
         <v>0.000808</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.005159</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.07564</v>
@@ -3914,28 +3870,28 @@
         <v>0</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>0.32134</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>0.588477</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>0.680685</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>0.690567</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>0.690567</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>0.690567</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>0.80183</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0</v>
+        <v>0.744791</v>
       </c>
       <c r="P56" s="3" t="n">
         <v>0</v>
@@ -3974,28 +3930,28 @@
         <v>0</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>0.055242</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>0.151207</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>0.276955</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>0.405682</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0</v>
+        <v>0.52498</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>0</v>
+        <v>0.591627</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>0</v>
+        <v>0.631283</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>0</v>
+        <v>0.635865</v>
       </c>
       <c r="P57" s="3" t="n">
         <v>0</v>
@@ -4400,31 +4356,31 @@
         <v>0</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.103028</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.111977</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.224264</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.414267</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.300629</v>
       </c>
       <c r="M64" s="3" t="n">
         <v>0.096765</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.378638</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.440108</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.529201</v>
       </c>
     </row>
     <row r="65">
@@ -4580,31 +4536,31 @@
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.356399</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.625481</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.73628</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.938084</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>1.112888</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.658543</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.867543</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>1.600443</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>2.100773</v>
       </c>
     </row>
     <row r="68">
@@ -6439,10 +6395,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C99" s="3" t="n">
+        <v>-0.066979</v>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
@@ -6503,10 +6457,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
@@ -6567,10 +6519,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
@@ -6631,10 +6581,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
@@ -6695,10 +6643,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
@@ -6759,10 +6705,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C104" s="3" t="n">
+        <v>0.018734</v>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
@@ -6823,10 +6767,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
@@ -6887,10 +6829,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C106" s="3" t="n">
+        <v>0.018734</v>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
@@ -6951,10 +6891,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
@@ -7015,10 +6953,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
@@ -7079,10 +7015,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
@@ -7143,10 +7077,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
@@ -7207,10 +7139,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
@@ -7233,16 +7163,16 @@
         </is>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.225431</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.467931</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.092208</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.009882</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
@@ -7271,10 +7201,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
@@ -7335,10 +7263,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
@@ -7399,10 +7325,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
@@ -7463,10 +7387,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
@@ -7513,7 +7435,7 @@
         <v>0</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.108677</v>
       </c>
     </row>
     <row r="116">
@@ -7527,10 +7449,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
@@ -7591,10 +7511,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
@@ -7655,10 +7573,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
@@ -7719,10 +7635,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
@@ -7783,10 +7697,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
@@ -7847,10 +7759,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
@@ -7911,10 +7821,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
@@ -7975,10 +7883,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
@@ -8039,10 +7945,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
@@ -8103,10 +8007,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
@@ -8167,10 +8069,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
@@ -8313,10 +8213,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C128" s="3" t="n">
+        <v>-0.039717</v>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
@@ -8377,10 +8275,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C129" s="3" t="n">
+        <v>0.285283</v>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
@@ -8441,10 +8337,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C130" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
@@ -8523,10 +8417,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
@@ -8587,10 +8479,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C132" s="3" t="n">
+        <v>0.237038</v>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
@@ -8651,10 +8541,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C133" s="3" t="n">
+        <v>0.237038</v>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
@@ -8733,10 +8621,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
@@ -8759,16 +8645,16 @@
         </is>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.225431</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.467931</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.092208</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.009882</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>0</v>
@@ -8797,10 +8683,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C135" s="3" t="n">
+        <v>-0.048245</v>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
@@ -8823,16 +8707,16 @@
         </is>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-1.596463</v>
+        <v>-1.821894</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-1.130461</v>
+        <v>-1.598392</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-0.730405</v>
+        <v>-0.822613</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-0.504082</v>
+        <v>-0.513964</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>-0.179208</v>
@@ -8861,7 +8745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S595"/>
+  <dimension ref="A1:S606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -22527,7 +22411,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -41029,10 +40917,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F360" s="5" t="n">
+        <v>-0.048245</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
@@ -41199,7 +41085,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -42918,10 +42808,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F381" s="5" t="n">
+        <v>0.325</v>
       </c>
       <c r="G381" t="inlineStr">
         <is>
@@ -43013,10 +42901,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F382" s="5" t="n">
+        <v>-0.039717</v>
       </c>
       <c r="G382" t="inlineStr">
         <is>
@@ -44679,25 +44565,31 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B401" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Cash flows from operating activities</t>
+        </is>
+      </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>March 31, 2025 March</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr"/>
+          <t>Net loss for the period</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E401" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F401" s="5" t="n">
+        <v>-0.066979</v>
       </c>
       <c r="G401" t="inlineStr">
         <is>
@@ -44754,39 +44646,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R401" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="S401" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Sale of mineralized material (Note 23)</t>
-        </is>
-      </c>
-      <c r="D402" t="inlineStr"/>
+          <t>Increase in accounts payable</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E402" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F402" s="5" t="n">
+        <v>0.018734</v>
       </c>
       <c r="G402" t="inlineStr">
         <is>
@@ -44843,8 +44741,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R402" s="5" t="n">
-        <v>0.12098</v>
+      <c r="R402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S402" t="inlineStr">
         <is>
@@ -44855,22 +44755,22 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Net cash provided by financing activities</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -44878,10 +44778,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F403" s="5" t="n">
+        <v>0.285283</v>
       </c>
       <c r="G403" t="inlineStr">
         <is>
@@ -44938,32 +44836,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R403" s="5" t="n">
-        <v>0.185975</v>
-      </c>
-      <c r="S403" s="5" t="n">
-        <v>0.09607300000000001</v>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Net increase in cash</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -44971,10 +44873,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F404" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F404" s="5" t="n">
+        <v>0.237038</v>
       </c>
       <c r="G404" t="inlineStr">
         <is>
@@ -45001,52 +44901,66 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L404" s="5" t="n">
-        <v>0.215862</v>
-      </c>
-      <c r="M404" s="5" t="n">
-        <v>0.08558300000000001</v>
-      </c>
-      <c r="N404" s="5" t="n">
-        <v>0.050451</v>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O404" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P404" s="5" t="n">
-        <v>0.074696</v>
-      </c>
-      <c r="Q404" s="5" t="n">
-        <v>0.276199</v>
-      </c>
-      <c r="R404" s="5" t="n">
-        <v>0.114914</v>
-      </c>
-      <c r="S404" s="5" t="n">
-        <v>0.125148</v>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>Cash, beginning of the period</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -45084,11 +44998,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L405" s="5" t="n">
-        <v>0.067606</v>
-      </c>
-      <c r="M405" s="5" t="n">
-        <v>0.062806</v>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N405" t="inlineStr">
         <is>
@@ -45105,35 +45023,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q405" s="5" t="n">
-        <v>0.086933</v>
-      </c>
-      <c r="R405" s="5" t="n">
-        <v>0.135336</v>
-      </c>
-      <c r="S405" s="5" t="n">
-        <v>0.091561</v>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Depreciation (Note 10,12)</t>
+          <t>Cash, end of the period</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -45141,10 +45065,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F406" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F406" s="5" t="n">
+        <v>0.237038</v>
       </c>
       <c r="G406" t="inlineStr">
         <is>
@@ -45191,17 +45113,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P406" s="5" t="n">
-        <v>0.091515</v>
-      </c>
-      <c r="Q406" s="5" t="n">
-        <v>0.071212</v>
-      </c>
-      <c r="R406" s="5" t="n">
-        <v>0.064278</v>
-      </c>
-      <c r="S406" s="5" t="n">
-        <v>0.014911</v>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="407">
@@ -45210,21 +45140,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B407" t="inlineStr"/>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Management and consulting fees (Note 16)</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>March 31, 2025 March</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr">
         <is>
           <t>-</t>
@@ -45280,17 +45202,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P407" s="5" t="n">
-        <v>0.51171</v>
-      </c>
-      <c r="Q407" s="5" t="n">
-        <v>0.421735</v>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R407" s="5" t="n">
-        <v>0.59605</v>
+        <v>0.002024</v>
       </c>
       <c r="S407" s="5" t="n">
-        <v>0.635931</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="408">
@@ -45301,12 +45227,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Impairment of property and equipment (Note 12)</t>
+          <t>Sale of mineralized material (Note 23)</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
@@ -45370,11 +45296,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q408" s="5" t="n">
-        <v>0.033069</v>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R408" s="5" t="n">
-        <v>0.107223</v>
+        <v>0.12098</v>
       </c>
       <c r="S408" t="inlineStr">
         <is>
@@ -45395,10 +45323,14 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets (Note 13)</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr"/>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
           <t>-</t>
@@ -45465,10 +45397,10 @@
         </is>
       </c>
       <c r="R409" s="5" t="n">
-        <v>0.09753299999999999</v>
+        <v>0.185975</v>
       </c>
       <c r="S409" s="5" t="n">
-        <v>0.003797</v>
+        <v>0.09607300000000001</v>
       </c>
     </row>
     <row r="410">
@@ -45484,10 +45416,14 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Impairment of inventory</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
           <t>-</t>
@@ -45523,43 +45459,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L410" s="5" t="n">
+        <v>0.215862</v>
+      </c>
+      <c r="M410" s="5" t="n">
+        <v>0.08558300000000001</v>
+      </c>
+      <c r="N410" s="5" t="n">
+        <v>0.050451</v>
       </c>
       <c r="O410" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P410" s="5" t="n">
+        <v>0.074696</v>
+      </c>
+      <c r="Q410" s="5" t="n">
+        <v>0.276199</v>
+      </c>
+      <c r="R410" s="5" t="n">
+        <v>0.114914</v>
       </c>
       <c r="S410" s="5" t="n">
-        <v>0.014126</v>
+        <v>0.125148</v>
       </c>
     </row>
     <row r="411">
@@ -45575,10 +45499,14 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Transfer, filing and listing fees</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr"/>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -45615,30 +45543,34 @@
         </is>
       </c>
       <c r="L411" s="5" t="n">
-        <v>0.05473</v>
+        <v>0.067606</v>
       </c>
       <c r="M411" s="5" t="n">
-        <v>0.047853</v>
-      </c>
-      <c r="N411" s="5" t="n">
-        <v>0.028274</v>
+        <v>0.062806</v>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O411" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P411" s="5" t="n">
-        <v>0.013262</v>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q411" s="5" t="n">
-        <v>0.043489</v>
+        <v>0.086933</v>
       </c>
       <c r="R411" s="5" t="n">
-        <v>0.026705</v>
+        <v>0.135336</v>
       </c>
       <c r="S411" s="5" t="n">
-        <v>0.037624</v>
+        <v>0.091561</v>
       </c>
     </row>
     <row r="412">
@@ -45654,10 +45586,14 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 16, 21)</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr"/>
+          <t>Depreciation (Note 10,12)</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>
@@ -45713,21 +45649,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P412" s="5" t="n">
+        <v>0.091515</v>
+      </c>
+      <c r="Q412" s="5" t="n">
+        <v>0.071212</v>
       </c>
       <c r="R412" s="5" t="n">
-        <v>0.022017</v>
+        <v>0.064278</v>
       </c>
       <c r="S412" s="5" t="n">
-        <v>0.016212</v>
+        <v>0.014911</v>
       </c>
     </row>
     <row r="413">
@@ -45743,10 +45675,14 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Accretion of interest (Note 17, 20)</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr"/>
+          <t>Management and consulting fees (Note 16)</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
           <t>-</t>
@@ -45802,21 +45738,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P413" s="5" t="n">
+        <v>0.51171</v>
+      </c>
+      <c r="Q413" s="5" t="n">
+        <v>0.421735</v>
       </c>
       <c r="R413" s="5" t="n">
-        <v>0.099444</v>
+        <v>0.59605</v>
       </c>
       <c r="S413" s="5" t="n">
-        <v>0.116914</v>
+        <v>0.635931</v>
       </c>
     </row>
     <row r="414">
@@ -45832,14 +45764,10 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Interest expense (Note 18, 20)</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Impairment of property and equipment (Note 12)</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -45900,16 +45828,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q414" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q414" s="5" t="n">
+        <v>0.033069</v>
       </c>
       <c r="R414" s="5" t="n">
-        <v>0.031754</v>
-      </c>
-      <c r="S414" s="5" t="n">
-        <v>0.039237</v>
+        <v>0.107223</v>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="415">
@@ -45925,7 +45853,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Gain from write-off of accounts payable</t>
+          <t>Impairment of exploration and evaluation assets (Note 13)</t>
         </is>
       </c>
       <c r="D415" t="inlineStr"/>
@@ -45994,13 +45922,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R415" s="5" t="n">
+        <v>0.09753299999999999</v>
       </c>
       <c r="S415" s="5" t="n">
-        <v>-0.028</v>
+        <v>0.003797</v>
       </c>
     </row>
     <row r="416">
@@ -46016,7 +45942,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Gain on fair value change on ACOA Loans (Note 17)</t>
+          <t>Impairment of inventory</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
@@ -46080,14 +46006,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q416" s="5" t="n">
-        <v>-0.099188</v>
-      </c>
-      <c r="R416" s="5" t="n">
-        <v>-0.09760099999999999</v>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S416" s="5" t="n">
-        <v>-0.039656</v>
+        <v>0.014126</v>
       </c>
     </row>
     <row r="417">
@@ -46103,14 +46033,10 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Loss (gain) on foreign exchange</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>ForeignExchangeTradingGains</t>
-        </is>
-      </c>
+          <t>Transfer, filing and listing fees</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -46146,39 +46072,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L417" s="5" t="n">
+        <v>0.05473</v>
+      </c>
+      <c r="M417" s="5" t="n">
+        <v>0.047853</v>
+      </c>
+      <c r="N417" s="5" t="n">
+        <v>0.028274</v>
       </c>
       <c r="O417" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P417" s="5" t="n">
+        <v>0.013262</v>
       </c>
       <c r="Q417" s="5" t="n">
-        <v>0.017269</v>
+        <v>0.043489</v>
       </c>
       <c r="R417" s="5" t="n">
-        <v>-0.001471</v>
+        <v>0.026705</v>
       </c>
       <c r="S417" s="5" t="n">
-        <v>0.035791</v>
+        <v>0.037624</v>
       </c>
     </row>
     <row r="418">
@@ -46194,14 +46112,10 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Share-based compensation (Note 16, 21)</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>
@@ -46237,31 +46151,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L418" s="5" t="n">
-        <v>1.758714</v>
-      </c>
-      <c r="M418" s="5" t="n">
-        <v>1.413931</v>
-      </c>
-      <c r="N418" s="5" t="n">
-        <v>1.126073</v>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O418" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P418" s="5" t="n">
-        <v>1.055858</v>
-      </c>
-      <c r="Q418" s="5" t="n">
-        <v>1.596841</v>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R418" s="5" t="n">
-        <v>1.382157</v>
+        <v>0.022017</v>
       </c>
       <c r="S418" s="5" t="n">
-        <v>1.159669</v>
+        <v>0.016212</v>
       </c>
     </row>
     <row r="419">
@@ -46272,12 +46196,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Other Income and loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Licensing income (Note 24)</t>
+          <t>Accretion of interest (Note 17, 20)</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
@@ -46346,13 +46270,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R419" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R419" s="5" t="n">
+        <v>0.099444</v>
       </c>
       <c r="S419" s="5" t="n">
-        <v>0.3</v>
+        <v>0.116914</v>
       </c>
     </row>
     <row r="420">
@@ -46363,15 +46285,19 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Other Income and loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Loss on sale of marketable securities (Note 15)</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr"/>
+          <t>Interest expense (Note 18, 20)</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
@@ -46437,13 +46363,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R420" s="5" t="n">
+        <v>0.031754</v>
       </c>
       <c r="S420" s="5" t="n">
-        <v>-0.041399</v>
+        <v>0.039237</v>
       </c>
     </row>
     <row r="421">
@@ -46454,12 +46378,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Other Income and loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Loss on extinguishment of convertible loan payable (Note 20)</t>
+          <t>Gain from write-off of accounts payable</t>
         </is>
       </c>
       <c r="D421" t="inlineStr"/>
@@ -46534,7 +46458,7 @@
         </is>
       </c>
       <c r="S421" s="5" t="n">
-        <v>-0.003925</v>
+        <v>-0.028</v>
       </c>
     </row>
     <row r="422">
@@ -46545,12 +46469,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Other Income and loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Gain from sale of property and equipment (Note 12)</t>
+          <t>Gain on fair value change on ACOA Loans (Note 17)</t>
         </is>
       </c>
       <c r="D422" t="inlineStr"/>
@@ -46614,18 +46538,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q422" s="5" t="n">
+        <v>-0.099188</v>
+      </c>
+      <c r="R422" s="5" t="n">
+        <v>-0.09760099999999999</v>
       </c>
       <c r="S422" s="5" t="n">
-        <v>0.05</v>
+        <v>-0.039656</v>
       </c>
     </row>
     <row r="423">
@@ -46636,15 +46556,19 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Other Income and loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Unrealized loss on marketable securities (Note 15)</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr"/>
+          <t>Loss (gain) on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
@@ -46705,18 +46629,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q423" s="5" t="n">
+        <v>0.017269</v>
+      </c>
+      <c r="R423" s="5" t="n">
+        <v>-0.001471</v>
       </c>
       <c r="S423" s="5" t="n">
-        <v>-0.149925</v>
+        <v>0.035791</v>
       </c>
     </row>
     <row r="424">
@@ -46727,15 +46647,19 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Other Income and loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Total other income (loss)</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr"/>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
           <t>-</t>
@@ -46771,43 +46695,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L424" s="5" t="n">
+        <v>1.758714</v>
+      </c>
+      <c r="M424" s="5" t="n">
+        <v>1.413931</v>
+      </c>
+      <c r="N424" s="5" t="n">
+        <v>1.126073</v>
       </c>
       <c r="O424" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P424" s="5" t="n">
+        <v>1.055858</v>
+      </c>
+      <c r="Q424" s="5" t="n">
+        <v>1.596841</v>
+      </c>
+      <c r="R424" s="5" t="n">
+        <v>1.382157</v>
       </c>
       <c r="S424" s="5" t="n">
-        <v>0.154751</v>
+        <v>1.159669</v>
       </c>
     </row>
     <row r="425">
@@ -46823,14 +46735,10 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Total loss for the year</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Licensing income (Note 24)</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr">
         <is>
           <t>-</t>
@@ -46896,11 +46804,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R425" s="5" t="n">
-        <v>-1.261177</v>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S425" s="5" t="n">
-        <v>-1.004918</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="426">
@@ -46911,12 +46821,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Other Income and loss</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Items that may be reclassified to profit and loss - cumulative translation adjustment</t>
+          <t>Loss on sale of marketable securities (Note 15)</t>
         </is>
       </c>
       <c r="D426" t="inlineStr"/>
@@ -46985,11 +46895,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R426" s="5" t="n">
-        <v>-0.000987</v>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S426" s="5" t="n">
-        <v>0.044792</v>
+        <v>-0.041399</v>
       </c>
     </row>
     <row r="427">
@@ -47000,19 +46912,15 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Other Income and loss</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Loss on extinguishment of convertible loan payable (Note 20)</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -47068,17 +46976,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P427" s="5" t="n">
-        <v>-0.959101</v>
-      </c>
-      <c r="Q427" s="5" t="n">
-        <v>-1.574591</v>
-      </c>
-      <c r="R427" s="5" t="n">
-        <v>-1.262164</v>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S427" s="5" t="n">
-        <v>-0.960126</v>
+        <v>-0.003925</v>
       </c>
     </row>
     <row r="428">
@@ -47089,19 +47003,15 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Other Income and loss</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Loss per share – Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Gain from sale of property and equipment (Note 12)</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -47157,17 +47067,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P428" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="Q428" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="R428" s="5" t="n">
-        <v>-8e-08</v>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S428" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="429">
@@ -47178,12 +47094,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Weighted average number of outstanding common shares</t>
+          <t>Other Income and loss</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>– Basic and diluted</t>
+          <t>Unrealized loss on marketable securities (Note 15)</t>
         </is>
       </c>
       <c r="D429" t="inlineStr"/>
@@ -47252,11 +47168,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R429" s="5" t="n">
-        <v>16.671879</v>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S429" s="5" t="n">
-        <v>17.037699</v>
+        <v>-0.149925</v>
       </c>
     </row>
     <row r="430">
@@ -47267,12 +47185,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>-See Accompanying Notes-</t>
+          <t>Other Income and loss</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Deficit $ - - - - - - - - - consolidated (25,218,237) (1,261,177) (26,479,414)</t>
+          <t>Total other income (loss)</t>
         </is>
       </c>
       <c r="D430" t="inlineStr"/>
@@ -47341,11 +47259,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R430" s="5" t="n">
-        <v>-27.484332</v>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S430" s="5" t="n">
-        <v>-1.004918</v>
+        <v>0.154751</v>
       </c>
     </row>
     <row r="431">
@@ -47356,15 +47276,19 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>These</t>
+          <t>Other Income and loss</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>These</t>
-        </is>
-      </c>
-      <c r="D431" t="inlineStr"/>
+          <t>Total loss for the year</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
           <t>-</t>
@@ -47430,15 +47354,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R431" s="5" t="n">
+        <v>-1.261177</v>
+      </c>
+      <c r="S431" s="5" t="n">
+        <v>-1.004918</v>
       </c>
     </row>
     <row r="432">
@@ -47449,12 +47369,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>(1)</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>$ - - - - - - - - Accompanying Capital 150,000 (36,162) 180,780 pre-consolidated -See 20,317,544</t>
+          <t>Items that may be reclassified to profit and loss - cumulative translation adjustment</t>
         </is>
       </c>
       <c r="D432" t="inlineStr"/>
@@ -47524,10 +47444,10 @@
         </is>
       </c>
       <c r="R432" s="5" t="n">
-        <v>20.612162</v>
+        <v>-0.000987</v>
       </c>
       <c r="S432" s="5" t="n">
-        <v>20.612162</v>
+        <v>0.044792</v>
       </c>
     </row>
     <row r="433">
@@ -47536,13 +47456,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B433" t="inlineStr"/>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>March 31, 2024 March</t>
-        </is>
-      </c>
-      <c r="D433" t="inlineStr"/>
+          <t>Comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -47598,21 +47526,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P433" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P433" s="5" t="n">
+        <v>-0.959101</v>
       </c>
       <c r="Q433" s="5" t="n">
-        <v>0.002023</v>
+        <v>-1.574591</v>
       </c>
       <c r="R433" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="S433" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.262164</v>
+      </c>
+      <c r="S433" s="5" t="n">
+        <v>-0.960126</v>
       </c>
     </row>
     <row r="434">
@@ -47623,15 +47547,19 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Sale of mineralized material (Note 21)</t>
-        </is>
-      </c>
-      <c r="D434" t="inlineStr"/>
+          <t>Loss per share – Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
           <t>-</t>
@@ -47687,23 +47615,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P434" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q434" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P434" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="Q434" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="R434" s="5" t="n">
-        <v>0.12098</v>
-      </c>
-      <c r="S434" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8e-08</v>
+      </c>
+      <c r="S434" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
       </c>
     </row>
     <row r="435">
@@ -47714,12 +47636,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of outstanding common shares</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Research, development and investigation expense</t>
+          <t>– Basic and diluted</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
@@ -47778,21 +47700,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P435" s="5" t="n">
-        <v>0.169237</v>
-      </c>
-      <c r="Q435" s="5" t="n">
-        <v>0.020709</v>
-      </c>
-      <c r="R435" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S435" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R435" s="5" t="n">
+        <v>16.671879</v>
+      </c>
+      <c r="S435" s="5" t="n">
+        <v>17.037699</v>
       </c>
     </row>
     <row r="436">
@@ -47803,19 +47725,15 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>-See Accompanying Notes-</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Management and consulting fees (Note 15)</t>
-        </is>
-      </c>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Deficit $ - - - - - - - - - consolidated (25,218,237) (1,261,177) (26,479,414)</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
           <t>-</t>
@@ -47876,16 +47794,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q436" s="5" t="n">
-        <v>0.421735</v>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R436" s="5" t="n">
-        <v>0.59605</v>
-      </c>
-      <c r="S436" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-27.484332</v>
+      </c>
+      <c r="S436" s="5" t="n">
+        <v>-1.004918</v>
       </c>
     </row>
     <row r="437">
@@ -47896,12 +47814,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>These</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Impairment (Note 13)</t>
+          <t>These</t>
         </is>
       </c>
       <c r="D437" t="inlineStr"/>
@@ -47970,8 +47888,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R437" s="5" t="n">
-        <v>0.09753299999999999</v>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S437" t="inlineStr">
         <is>
@@ -47987,12 +47907,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>(1)</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 15,19)</t>
+          <t>$ - - - - - - - - Accompanying Capital 150,000 (36,162) 180,780 pre-consolidated -See 20,317,544</t>
         </is>
       </c>
       <c r="D438" t="inlineStr"/>
@@ -48056,16 +47976,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q438" s="5" t="n">
-        <v>0.6146509999999999</v>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R438" s="5" t="n">
-        <v>0.022017</v>
-      </c>
-      <c r="S438" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>20.612162</v>
+      </c>
+      <c r="S438" s="5" t="n">
+        <v>20.612162</v>
       </c>
     </row>
     <row r="439">
@@ -48074,14 +47994,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B439" t="inlineStr"/>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Accretion of interest (Note 16,18)</t>
+          <t>March 31, 2024 March</t>
         </is>
       </c>
       <c r="D439" t="inlineStr"/>
@@ -48146,10 +48062,10 @@
         </is>
       </c>
       <c r="Q439" s="5" t="n">
-        <v>0.103425</v>
+        <v>0.002023</v>
       </c>
       <c r="R439" s="5" t="n">
-        <v>0.099444</v>
+        <v>3.1e-05</v>
       </c>
       <c r="S439" t="inlineStr">
         <is>
@@ -48165,19 +48081,15 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Interest expense (Note 17, 18)</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Sale of mineralized material (Note 21)</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr"/>
       <c r="E440" t="inlineStr">
         <is>
           <t>-</t>
@@ -48238,11 +48150,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q440" s="5" t="n">
-        <v>0.007338</v>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R440" s="5" t="n">
-        <v>0.031754</v>
+        <v>0.12098</v>
       </c>
       <c r="S440" t="inlineStr">
         <is>
@@ -48263,7 +48177,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Gain on fair value change on ACOA Loans (Note 16)</t>
+          <t>Research, development and investigation expense</t>
         </is>
       </c>
       <c r="D441" t="inlineStr"/>
@@ -48322,16 +48236,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P441" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P441" s="5" t="n">
+        <v>0.169237</v>
       </c>
       <c r="Q441" s="5" t="n">
-        <v>-0.099188</v>
-      </c>
-      <c r="R441" s="5" t="n">
-        <v>-0.09760099999999999</v>
+        <v>0.020709</v>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S441" t="inlineStr">
         <is>
@@ -48352,12 +48266,12 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Total loss for the year</t>
+          <t>Management and consulting fees (Note 15)</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -48421,10 +48335,10 @@
         </is>
       </c>
       <c r="Q442" s="5" t="n">
-        <v>-1.596841</v>
+        <v>0.421735</v>
       </c>
       <c r="R442" s="5" t="n">
-        <v>-1.261177</v>
+        <v>0.59605</v>
       </c>
       <c r="S442" t="inlineStr">
         <is>
@@ -48440,12 +48354,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Items that may be reclassified to profit and loss cumulative translation adjustment</t>
+          <t>Impairment (Note 13)</t>
         </is>
       </c>
       <c r="D443" t="inlineStr"/>
@@ -48504,14 +48418,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P443" s="5" t="n">
-        <v>-8e-06</v>
-      </c>
-      <c r="Q443" s="5" t="n">
-        <v>0.02225</v>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R443" s="5" t="n">
-        <v>-0.000987</v>
+        <v>0.09753299999999999</v>
       </c>
       <c r="S443" t="inlineStr">
         <is>
@@ -48527,19 +48445,15 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Share-based compensation (Note 15,19)</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr"/>
       <c r="E444" t="inlineStr">
         <is>
           <t>-</t>
@@ -48601,10 +48515,10 @@
         </is>
       </c>
       <c r="Q444" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.6146509999999999</v>
       </c>
       <c r="R444" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.022017</v>
       </c>
       <c r="S444" t="inlineStr">
         <is>
@@ -48620,12 +48534,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Weighted average number of outstanding common shares –</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Accretion of interest (Note 16,18)</t>
         </is>
       </c>
       <c r="D445" t="inlineStr"/>
@@ -48684,14 +48598,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P445" s="5" t="n">
-        <v>119.201269</v>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q445" s="5" t="n">
-        <v>159.645397</v>
+        <v>0.103425</v>
       </c>
       <c r="R445" s="5" t="n">
-        <v>166.718794</v>
+        <v>0.099444</v>
       </c>
       <c r="S445" t="inlineStr">
         <is>
@@ -48707,15 +48623,19 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>(#)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Balance – March 31, 2022 153,337,013 19,605,266 3,872,789 (8)</t>
-        </is>
-      </c>
-      <c r="D446" t="inlineStr"/>
+          <t>Interest expense (Note 17, 18)</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
           <t>-</t>
@@ -48777,10 +48697,10 @@
         </is>
       </c>
       <c r="Q446" s="5" t="n">
-        <v>-0.143349</v>
+        <v>0.007338</v>
       </c>
       <c r="R446" s="5" t="n">
-        <v>-23.621396</v>
+        <v>0.031754</v>
       </c>
       <c r="S446" t="inlineStr">
         <is>
@@ -48796,12 +48716,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Private placement, net of issuance cost</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>(Note 19) 14,040,000 627,540 70,200 -</t>
+          <t>Gain on fair value change on ACOA Loans (Note 16)</t>
         </is>
       </c>
       <c r="D447" t="inlineStr"/>
@@ -48866,12 +48786,10 @@
         </is>
       </c>
       <c r="Q447" s="5" t="n">
-        <v>0.69774</v>
-      </c>
-      <c r="R447" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.099188</v>
+      </c>
+      <c r="R447" s="5" t="n">
+        <v>-0.09760099999999999</v>
       </c>
       <c r="S447" t="inlineStr">
         <is>
@@ -48887,15 +48805,19 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Fair value recognized for the shares issued for</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Fair value recognized for the shares issued for acquisition of mineral properties (Note 13) - 84,738 - -</t>
-        </is>
-      </c>
-      <c r="D448" t="inlineStr"/>
+          <t>Total loss for the year</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
           <t>-</t>
@@ -48951,16 +48873,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P448" s="5" t="n">
-        <v>0.08473799999999999</v>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q448" s="5" t="n">
-        <v>0.08473799999999999</v>
-      </c>
-      <c r="R448" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.596841</v>
+      </c>
+      <c r="R448" s="5" t="n">
+        <v>-1.261177</v>
       </c>
       <c r="S448" t="inlineStr">
         <is>
@@ -48976,12 +48898,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Fair value recognized for the shares issued for</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 19) - - 614,651 -</t>
+          <t>Items that may be reclassified to profit and loss cumulative translation adjustment</t>
         </is>
       </c>
       <c r="D449" t="inlineStr"/>
@@ -49040,18 +48962,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P449" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P449" s="5" t="n">
+        <v>-8e-06</v>
       </c>
       <c r="Q449" s="5" t="n">
-        <v>0.6146509999999999</v>
-      </c>
-      <c r="R449" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.02225</v>
+      </c>
+      <c r="R449" s="5" t="n">
+        <v>-0.000987</v>
       </c>
       <c r="S449" t="inlineStr">
         <is>
@@ -49067,15 +48985,19 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Fair value recognized for the shares issued for</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Translation adjustment - - - 22,250</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr"/>
+          <t>Loss per share – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
           <t>-</t>
@@ -49131,16 +49053,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P450" s="5" t="n">
-        <v>0.02225</v>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q450" s="5" t="n">
-        <v>0.02225</v>
-      </c>
-      <c r="R450" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="R450" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="S450" t="inlineStr">
         <is>
@@ -49156,19 +49078,15 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Fair value recognized for the shares issued for</t>
+          <t>Weighted average number of outstanding common shares –</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - -</t>
-        </is>
-      </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr">
         <is>
           <t>-</t>
@@ -49225,13 +49143,13 @@
         </is>
       </c>
       <c r="P451" s="5" t="n">
-        <v>-1.596841</v>
+        <v>119.201269</v>
       </c>
       <c r="Q451" s="5" t="n">
-        <v>-1.596841</v>
+        <v>159.645397</v>
       </c>
       <c r="R451" s="5" t="n">
-        <v>-1.596841</v>
+        <v>166.718794</v>
       </c>
       <c r="S451" t="inlineStr">
         <is>
@@ -49247,12 +49165,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Fair value recognized for the shares issued for</t>
+          <t>(#)</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Balance- March 31, 2023 167,377,013 20,317,544 4,557,640 22,242</t>
+          <t>Balance – March 31, 2022 153,337,013 19,605,266 3,872,789 (8)</t>
         </is>
       </c>
       <c r="D452" t="inlineStr"/>
@@ -49311,14 +49229,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P452" s="5" t="n">
-        <v>-0.320811</v>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q452" s="5" t="n">
-        <v>-0.320811</v>
+        <v>-0.143349</v>
       </c>
       <c r="R452" s="5" t="n">
-        <v>-25.218237</v>
+        <v>-23.621396</v>
       </c>
       <c r="S452" t="inlineStr">
         <is>
@@ -49334,12 +49254,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Fair value recognized for the shares issued for</t>
+          <t>Private placement, net of issuance cost</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Stock options exercised 3,000,000 150,000 - -</t>
+          <t>(Note 19) 14,040,000 627,540 70,200 -</t>
         </is>
       </c>
       <c r="D453" t="inlineStr"/>
@@ -49404,7 +49324,7 @@
         </is>
       </c>
       <c r="Q453" s="5" t="n">
-        <v>0.15</v>
+        <v>0.69774</v>
       </c>
       <c r="R453" t="inlineStr">
         <is>
@@ -49430,7 +49350,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Fair value recognized for the shares issued for acquisition of mineral properties (note 13) - (36,161) - -</t>
+          <t>Fair value recognized for the shares issued for acquisition of mineral properties (Note 13) - 84,738 - -</t>
         </is>
       </c>
       <c r="D454" t="inlineStr"/>
@@ -49489,13 +49409,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P454" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P454" s="5" t="n">
+        <v>0.08473799999999999</v>
       </c>
       <c r="Q454" s="5" t="n">
-        <v>-0.036161</v>
+        <v>0.08473799999999999</v>
       </c>
       <c r="R454" t="inlineStr">
         <is>
@@ -49516,12 +49434,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Fair value adjustment for options exercised</t>
+          <t>Fair value recognized for the shares issued for</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Fair value adjustment for options exercised and cancelled (Note 19) - 180,780 (180,780) -</t>
+          <t>Share-based compensation (Note 19) - - 614,651 -</t>
         </is>
       </c>
       <c r="D455" t="inlineStr"/>
@@ -49585,10 +49503,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q455" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q455" s="5" t="n">
+        <v>0.6146509999999999</v>
       </c>
       <c r="R455" t="inlineStr">
         <is>
@@ -49609,12 +49525,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Fair value adjustment for options exercised</t>
+          <t>Fair value recognized for the shares issued for</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 19) - - 22,017 -</t>
+          <t>Translation adjustment - - - 22,250</t>
         </is>
       </c>
       <c r="D456" t="inlineStr"/>
@@ -49673,13 +49589,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P456" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P456" s="5" t="n">
+        <v>0.02225</v>
       </c>
       <c r="Q456" s="5" t="n">
-        <v>0.022017</v>
+        <v>0.02225</v>
       </c>
       <c r="R456" t="inlineStr">
         <is>
@@ -49700,15 +49614,19 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Fair value adjustment for options exercised</t>
+          <t>Fair value recognized for the shares issued for</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Translation adjustment - - - (987)</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr"/>
+          <t>Net loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>
@@ -49764,18 +49682,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P457" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P457" s="5" t="n">
+        <v>-1.596841</v>
       </c>
       <c r="Q457" s="5" t="n">
-        <v>-0.000987</v>
-      </c>
-      <c r="R457" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.596841</v>
+      </c>
+      <c r="R457" s="5" t="n">
+        <v>-1.596841</v>
       </c>
       <c r="S457" t="inlineStr">
         <is>
@@ -49791,19 +49705,15 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Fair value adjustment for options exercised</t>
+          <t>Fair value recognized for the shares issued for</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - -</t>
-        </is>
-      </c>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance- March 31, 2023 167,377,013 20,317,544 4,557,640 22,242</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr">
         <is>
           <t>-</t>
@@ -49859,16 +49769,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P458" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P458" s="5" t="n">
+        <v>-0.320811</v>
       </c>
       <c r="Q458" s="5" t="n">
-        <v>-1.261177</v>
+        <v>-0.320811</v>
       </c>
       <c r="R458" s="5" t="n">
-        <v>-1.261177</v>
+        <v>-25.218237</v>
       </c>
       <c r="S458" t="inlineStr">
         <is>
@@ -49884,12 +49792,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Fair value adjustment for options exercised</t>
+          <t>Fair value recognized for the shares issued for</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Balance- March 31, 2024 170,377,013 20,612,162 4,398,877 21,255</t>
+          <t>Stock options exercised 3,000,000 150,000 - -</t>
         </is>
       </c>
       <c r="D459" t="inlineStr"/>
@@ -49954,10 +49862,12 @@
         </is>
       </c>
       <c r="Q459" s="5" t="n">
-        <v>-1.44712</v>
-      </c>
-      <c r="R459" s="5" t="n">
-        <v>-26.479414</v>
+        <v>0.15</v>
+      </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S459" t="inlineStr">
         <is>
@@ -49971,10 +49881,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B460" t="inlineStr"/>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Fair value recognized for the shares issued for</t>
+        </is>
+      </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>March 31, 2023 March</t>
+          <t>Fair value recognized for the shares issued for acquisition of mineral properties (note 13) - (36,161) - -</t>
         </is>
       </c>
       <c r="D460" t="inlineStr"/>
@@ -50033,11 +49947,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P460" s="5" t="n">
-        <v>0.002022</v>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q460" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>-0.036161</v>
       </c>
       <c r="R460" t="inlineStr">
         <is>
@@ -50058,19 +49974,15 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Fair value adjustment for options exercised</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>General and administrative expenses (Note 16)</t>
-        </is>
-      </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Fair value adjustment for options exercised and cancelled (Note 19) - 180,780 (180,780) -</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr">
         <is>
           <t>-</t>
@@ -50126,11 +50038,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P461" s="5" t="n">
-        <v>0.049202</v>
-      </c>
-      <c r="Q461" s="5" t="n">
-        <v>0.086933</v>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R461" t="inlineStr">
         <is>
@@ -50151,12 +50067,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Fair value adjustment for options exercised</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Share based compensation (Note 16,20)</t>
+          <t>Share-based compensation (Note 19) - - 22,017 -</t>
         </is>
       </c>
       <c r="D462" t="inlineStr"/>
@@ -50221,7 +50137,7 @@
         </is>
       </c>
       <c r="Q462" s="5" t="n">
-        <v>0.6146509999999999</v>
+        <v>0.022017</v>
       </c>
       <c r="R462" t="inlineStr">
         <is>
@@ -50242,12 +50158,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Fair value adjustment for options exercised</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Accretion of interest (Note 17,19)</t>
+          <t>Translation adjustment - - - (987)</t>
         </is>
       </c>
       <c r="D463" t="inlineStr"/>
@@ -50306,11 +50222,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P463" s="5" t="n">
-        <v>0.121859</v>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q463" s="5" t="n">
-        <v>0.103425</v>
+        <v>-0.000987</v>
       </c>
       <c r="R463" t="inlineStr">
         <is>
@@ -50331,17 +50249,17 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Fair value adjustment for options exercised</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Interest expense (Note 18)</t>
+          <t>Net loss for the year - - - -</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -50399,16 +50317,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P464" s="5" t="n">
-        <v>0.016914</v>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q464" s="5" t="n">
-        <v>0.007338</v>
-      </c>
-      <c r="R464" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.261177</v>
+      </c>
+      <c r="R464" s="5" t="n">
+        <v>-1.261177</v>
       </c>
       <c r="S464" t="inlineStr">
         <is>
@@ -50424,19 +50342,15 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Fair value adjustment for options exercised</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Loss on foreign exchange</t>
-        </is>
-      </c>
-      <c r="D465" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Balance- March 31, 2024 170,377,013 20,612,162 4,398,877 21,255</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr">
         <is>
           <t>-</t>
@@ -50472,30 +50386,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L465" s="5" t="n">
-        <v>0.045312</v>
-      </c>
-      <c r="M465" s="5" t="n">
-        <v>0.017852</v>
-      </c>
-      <c r="N465" s="5" t="n">
-        <v>-0.000155</v>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O465" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P465" s="5" t="n">
-        <v>0.007463</v>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q465" s="5" t="n">
-        <v>0.017269</v>
-      </c>
-      <c r="R465" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.44712</v>
+      </c>
+      <c r="R465" s="5" t="n">
+        <v>-26.479414</v>
       </c>
       <c r="S465" t="inlineStr">
         <is>
@@ -50509,14 +50429,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>Other items</t>
-        </is>
-      </c>
+      <c r="B466" t="inlineStr"/>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Gain on forgiveness of accounts payable</t>
+          <t>March 31, 2023 March</t>
         </is>
       </c>
       <c r="D466" t="inlineStr"/>
@@ -50576,12 +50492,10 @@
         </is>
       </c>
       <c r="P466" s="5" t="n">
-        <v>0.096765</v>
-      </c>
-      <c r="Q466" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002022</v>
+      </c>
+      <c r="Q466" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="R466" t="inlineStr">
         <is>
@@ -50602,17 +50516,17 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Total loss for the year</t>
+          <t>General and administrative expenses (Note 16)</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -50671,10 +50585,10 @@
         </is>
       </c>
       <c r="P467" s="5" t="n">
-        <v>-0.959093</v>
+        <v>0.049202</v>
       </c>
       <c r="Q467" s="5" t="n">
-        <v>-1.596841</v>
+        <v>0.086933</v>
       </c>
       <c r="R467" t="inlineStr">
         <is>
@@ -50695,12 +50609,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>(#)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Balance - March 31, 2021 90,443,313 16,657,789 3,872,789 -</t>
+          <t>Share based compensation (Note 16,20)</t>
         </is>
       </c>
       <c r="D468" t="inlineStr"/>
@@ -50759,11 +50673,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P468" s="5" t="n">
-        <v>-2.131725</v>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q468" s="5" t="n">
-        <v>-22.662303</v>
+        <v>0.6146509999999999</v>
       </c>
       <c r="R468" t="inlineStr">
         <is>
@@ -50784,12 +50700,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Shares issued for private placement, net of</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Shares issued for private placement, net of share issuance costs (note 20) 58,393,700 2,898,252 - -</t>
+          <t>Accretion of interest (Note 17,19)</t>
         </is>
       </c>
       <c r="D469" t="inlineStr"/>
@@ -50849,12 +50765,10 @@
         </is>
       </c>
       <c r="P469" s="5" t="n">
-        <v>2.898252</v>
-      </c>
-      <c r="Q469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.121859</v>
+      </c>
+      <c r="Q469" s="5" t="n">
+        <v>0.103425</v>
       </c>
       <c r="R469" t="inlineStr">
         <is>
@@ -50875,15 +50789,19 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Shares issued for acquisition of mineral</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Shares issued for acquisition of mineral properties (note 13) 4,500,000 49,225 - -</t>
-        </is>
-      </c>
-      <c r="D470" t="inlineStr"/>
+          <t>Interest expense (Note 18)</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E470" t="inlineStr">
         <is>
           <t>-</t>
@@ -50940,12 +50858,10 @@
         </is>
       </c>
       <c r="P470" s="5" t="n">
-        <v>0.049225</v>
-      </c>
-      <c r="Q470" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.016914</v>
+      </c>
+      <c r="Q470" s="5" t="n">
+        <v>0.007338</v>
       </c>
       <c r="R470" t="inlineStr">
         <is>
@@ -50966,15 +50882,19 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Shares issued for acquisition of mineral</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Translation adjustment - - - (8)</t>
-        </is>
-      </c>
-      <c r="D471" t="inlineStr"/>
+          <t>Loss on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E471" t="inlineStr">
         <is>
           <t>-</t>
@@ -51010,20 +50930,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L471" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M471" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N471" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L471" s="5" t="n">
+        <v>0.045312</v>
+      </c>
+      <c r="M471" s="5" t="n">
+        <v>0.017852</v>
+      </c>
+      <c r="N471" s="5" t="n">
+        <v>-0.000155</v>
       </c>
       <c r="O471" t="inlineStr">
         <is>
@@ -51031,12 +50945,10 @@
         </is>
       </c>
       <c r="P471" s="5" t="n">
-        <v>-8e-06</v>
-      </c>
-      <c r="Q471" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.007463</v>
+      </c>
+      <c r="Q471" s="5" t="n">
+        <v>0.017269</v>
       </c>
       <c r="R471" t="inlineStr">
         <is>
@@ -51057,19 +50969,15 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Shares issued for acquisition of mineral</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - -</t>
-        </is>
-      </c>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on forgiveness of accounts payable</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr">
         <is>
           <t>-</t>
@@ -51126,10 +51034,12 @@
         </is>
       </c>
       <c r="P472" s="5" t="n">
-        <v>-0.959093</v>
-      </c>
-      <c r="Q472" s="5" t="n">
-        <v>-0.959093</v>
+        <v>0.096765</v>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R472" t="inlineStr">
         <is>
@@ -51150,15 +51060,19 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Shares issued for acquisition of mineral</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Balance- March 31, 2022 153,337,013 19,605,266 3,872,789 (8)</t>
-        </is>
-      </c>
-      <c r="D473" t="inlineStr"/>
+          <t>Total loss for the year</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
           <t>-</t>
@@ -51215,10 +51129,10 @@
         </is>
       </c>
       <c r="P473" s="5" t="n">
-        <v>-0.143349</v>
+        <v>-0.959093</v>
       </c>
       <c r="Q473" s="5" t="n">
-        <v>-23.621396</v>
+        <v>-1.596841</v>
       </c>
       <c r="R473" t="inlineStr">
         <is>
@@ -51239,12 +51153,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Private placement, net of issuance cost</t>
+          <t>(#)</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>(Note 20) 14,040,000 627,540 70,200 -</t>
+          <t>Balance - March 31, 2021 90,443,313 16,657,789 3,872,789 -</t>
         </is>
       </c>
       <c r="D474" t="inlineStr"/>
@@ -51304,12 +51218,10 @@
         </is>
       </c>
       <c r="P474" s="5" t="n">
-        <v>0.69774</v>
-      </c>
-      <c r="Q474" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.131725</v>
+      </c>
+      <c r="Q474" s="5" t="n">
+        <v>-22.662303</v>
       </c>
       <c r="R474" t="inlineStr">
         <is>
@@ -51330,12 +51242,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Fair value recognized for the shares issued for</t>
+          <t>Shares issued for private placement, net of</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Share based compensation (Note 20) - - 614,651 -</t>
+          <t>Shares issued for private placement, net of share issuance costs (note 20) 58,393,700 2,898,252 - -</t>
         </is>
       </c>
       <c r="D475" t="inlineStr"/>
@@ -51395,7 +51307,7 @@
         </is>
       </c>
       <c r="P475" s="5" t="n">
-        <v>0.6146509999999999</v>
+        <v>2.898252</v>
       </c>
       <c r="Q475" t="inlineStr">
         <is>
@@ -51421,12 +51333,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares issued for acquisition of mineral</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Research and development, net of government grants and assistance (note 15)</t>
+          <t>Shares issued for acquisition of mineral properties (note 13) 4,500,000 49,225 - -</t>
         </is>
       </c>
       <c r="D476" t="inlineStr"/>
@@ -51465,24 +51377,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L476" s="5" t="n">
-        <v>0.238085</v>
-      </c>
-      <c r="M476" s="5" t="n">
-        <v>0.240025</v>
-      </c>
-      <c r="N476" s="5" t="n">
-        <v>0.21321</v>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O476" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P476" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P476" s="5" t="n">
+        <v>0.049225</v>
       </c>
       <c r="Q476" t="inlineStr">
         <is>
@@ -51508,19 +51424,15 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares issued for acquisition of mineral</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>General and administrative expenses (note 13)</t>
-        </is>
-      </c>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Translation adjustment - - - (8)</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
           <t>-</t>
@@ -51561,21 +51473,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M477" s="5" t="n">
-        <v>0.062806</v>
-      </c>
-      <c r="N477" s="5" t="n">
-        <v>0.0364</v>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O477" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P477" s="5" t="n">
+        <v>-8e-06</v>
       </c>
       <c r="Q477" t="inlineStr">
         <is>
@@ -51601,17 +51515,17 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares issued for acquisition of mineral</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Depreciation (notes 10,11)</t>
+          <t>Net loss for the year - - - -</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -51654,26 +51568,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M478" s="5" t="n">
-        <v>0.125748</v>
-      </c>
-      <c r="N478" s="5" t="n">
-        <v>0.166931</v>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O478" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P478" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q478" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P478" s="5" t="n">
+        <v>-0.959093</v>
+      </c>
+      <c r="Q478" s="5" t="n">
+        <v>-0.959093</v>
       </c>
       <c r="R478" t="inlineStr">
         <is>
@@ -51694,19 +51608,15 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares issued for acquisition of mineral</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Management and consulting fees (note 13)</t>
-        </is>
-      </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Balance- March 31, 2022 153,337,013 19,605,266 3,872,789 (8)</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
           <t>-</t>
@@ -51747,26 +51657,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M479" s="5" t="n">
-        <v>0.456889</v>
-      </c>
-      <c r="N479" s="5" t="n">
-        <v>0.516745</v>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O479" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P479" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q479" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P479" s="5" t="n">
+        <v>-0.143349</v>
+      </c>
+      <c r="Q479" s="5" t="n">
+        <v>-23.621396</v>
       </c>
       <c r="R479" t="inlineStr">
         <is>
@@ -51787,12 +51697,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Private placement, net of issuance cost</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Investor relations expense</t>
+          <t>(Note 20) 14,040,000 627,540 70,200 -</t>
         </is>
       </c>
       <c r="D480" t="inlineStr"/>
@@ -51831,11 +51741,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L480" s="5" t="n">
-        <v>0.093038</v>
-      </c>
-      <c r="M480" s="5" t="n">
-        <v>0.000378</v>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N480" t="inlineStr">
         <is>
@@ -51847,10 +51761,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P480" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P480" s="5" t="n">
+        <v>0.69774</v>
       </c>
       <c r="Q480" t="inlineStr">
         <is>
@@ -51876,12 +51788,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Fair value recognized for the shares issued for</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Stock-based compensation (notes 13,18)</t>
+          <t>Share based compensation (Note 20) - - 614,651 -</t>
         </is>
       </c>
       <c r="D481" t="inlineStr"/>
@@ -51925,8 +51837,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M481" s="5" t="n">
-        <v>0.269985</v>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N481" t="inlineStr">
         <is>
@@ -51938,10 +51852,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P481" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P481" s="5" t="n">
+        <v>0.6146509999999999</v>
       </c>
       <c r="Q481" t="inlineStr">
         <is>
@@ -51972,7 +51884,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Interest expense (income)</t>
+          <t>Research and development, net of government grants and assistance (note 15)</t>
         </is>
       </c>
       <c r="D482" t="inlineStr"/>
@@ -52011,16 +51923,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L482" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L482" s="5" t="n">
+        <v>0.238085</v>
       </c>
       <c r="M482" s="5" t="n">
-        <v>-0.00033</v>
+        <v>0.240025</v>
       </c>
       <c r="N482" s="5" t="n">
-        <v>0.010433</v>
+        <v>0.21321</v>
       </c>
       <c r="O482" t="inlineStr">
         <is>
@@ -52061,10 +51971,14 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Accretion of interest (note 15)</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr"/>
+          <t>General and administrative expenses (note 13)</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E483" t="inlineStr">
         <is>
           <t>-</t>
@@ -52100,14 +52014,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L483" s="5" t="n">
-        <v>0.040494</v>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M483" s="5" t="n">
-        <v>0.07432</v>
+        <v>0.062806</v>
       </c>
       <c r="N483" s="5" t="n">
-        <v>0.10556</v>
+        <v>0.0364</v>
       </c>
       <c r="O483" t="inlineStr">
         <is>
@@ -52148,10 +52064,14 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Realized and unrealized loss (gain) on marketable securities</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr"/>
+          <t>Depreciation (notes 10,11)</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E484" t="inlineStr">
         <is>
           <t>-</t>
@@ -52187,14 +52107,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L484" s="5" t="n">
-        <v>-0.002483</v>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M484" s="5" t="n">
-        <v>0.032166</v>
+        <v>0.125748</v>
       </c>
       <c r="N484" s="5" t="n">
-        <v>-0.001776</v>
+        <v>0.166931</v>
       </c>
       <c r="O484" t="inlineStr">
         <is>
@@ -52235,10 +52157,14 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Share of loss in investment using the equity method (note 12)</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr"/>
+          <t>Management and consulting fees (note 13)</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E485" t="inlineStr">
         <is>
           <t>-</t>
@@ -52280,12 +52206,10 @@
         </is>
       </c>
       <c r="M485" s="5" t="n">
-        <v>0.000656</v>
-      </c>
-      <c r="N485" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.456889</v>
+      </c>
+      <c r="N485" s="5" t="n">
+        <v>0.516745</v>
       </c>
       <c r="O485" t="inlineStr">
         <is>
@@ -52321,12 +52245,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Gain on write-off of accounts payable</t>
+          <t>Investor relations expense</t>
         </is>
       </c>
       <c r="D486" t="inlineStr"/>
@@ -52365,13 +52289,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L486" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L486" s="5" t="n">
+        <v>0.093038</v>
       </c>
       <c r="M486" s="5" t="n">
-        <v>0.173906</v>
+        <v>0.000378</v>
       </c>
       <c r="N486" t="inlineStr">
         <is>
@@ -52412,12 +52334,12 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Write-off of Pathaha Agro deposit (note 12)</t>
+          <t>Stock-based compensation (notes 13,18)</t>
         </is>
       </c>
       <c r="D487" t="inlineStr"/>
@@ -52462,7 +52384,7 @@
         </is>
       </c>
       <c r="M487" s="5" t="n">
-        <v>-0.120267</v>
+        <v>0.269985</v>
       </c>
       <c r="N487" t="inlineStr">
         <is>
@@ -52503,12 +52425,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Impairment of marketable securities</t>
+          <t>Interest expense (income)</t>
         </is>
       </c>
       <c r="D488" t="inlineStr"/>
@@ -52552,13 +52474,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M488" s="5" t="n">
+        <v>-0.00033</v>
       </c>
       <c r="N488" s="5" t="n">
-        <v>0.012119</v>
+        <v>0.010433</v>
       </c>
       <c r="O488" t="inlineStr">
         <is>
@@ -52594,12 +52514,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Impairment of investment in joint venture (note 12)</t>
+          <t>Accretion of interest (note 15)</t>
         </is>
       </c>
       <c r="D489" t="inlineStr"/>
@@ -52638,18 +52558,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L489" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L489" s="5" t="n">
+        <v>0.040494</v>
       </c>
       <c r="M489" s="5" t="n">
-        <v>-8.403320000000001</v>
-      </c>
-      <c r="N489" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.07432</v>
+      </c>
+      <c r="N489" s="5" t="n">
+        <v>0.10556</v>
       </c>
       <c r="O489" t="inlineStr">
         <is>
@@ -52685,19 +52601,15 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Realized and unrealized loss (gain) on marketable securities</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
         <is>
           <t>-</t>
@@ -52734,13 +52646,13 @@
         </is>
       </c>
       <c r="L490" s="5" t="n">
-        <v>-1.758714</v>
+        <v>-0.002483</v>
       </c>
       <c r="M490" s="5" t="n">
-        <v>-9.763612</v>
+        <v>0.032166</v>
       </c>
       <c r="N490" s="5" t="n">
-        <v>-1.138192</v>
+        <v>-0.001776</v>
       </c>
       <c r="O490" t="inlineStr">
         <is>
@@ -52776,12 +52688,12 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Translation adjustment</t>
+          <t>Share of loss in investment using the equity method (note 12)</t>
         </is>
       </c>
       <c r="D491" t="inlineStr"/>
@@ -52820,11 +52732,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L491" s="5" t="n">
-        <v>-0.482568</v>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M491" s="5" t="n">
-        <v>-0.618499</v>
+        <v>0.000656</v>
       </c>
       <c r="N491" t="inlineStr">
         <is>
@@ -52865,12 +52779,12 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Impairment of investment in joint venture</t>
+          <t>Gain on write-off of accounts payable</t>
         </is>
       </c>
       <c r="D492" t="inlineStr"/>
@@ -52915,7 +52829,7 @@
         </is>
       </c>
       <c r="M492" s="5" t="n">
-        <v>0.8181659999999999</v>
+        <v>0.173906</v>
       </c>
       <c r="N492" t="inlineStr">
         <is>
@@ -52956,19 +52870,15 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Write-off of Pathaha Agro deposit (note 12)</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr">
         <is>
           <t>-</t>
@@ -52999,17 +52909,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K493" s="5" t="n">
-        <v>-2.403702</v>
-      </c>
-      <c r="L493" s="5" t="n">
-        <v>-2.241282</v>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M493" s="5" t="n">
-        <v>-9.563945</v>
-      </c>
-      <c r="N493" s="5" t="n">
-        <v>-1.138192</v>
+        <v>-0.120267</v>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O493" t="inlineStr">
         <is>
@@ -53045,19 +52961,15 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Loss per share - Basic and diluted loss per share</t>
-        </is>
-      </c>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Impairment of marketable securities</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr">
         <is>
           <t>-</t>
@@ -53088,17 +53000,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K494" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="L494" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="M494" s="5" t="n">
-        <v>-1.1e-07</v>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N494" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.012119</v>
       </c>
       <c r="O494" t="inlineStr">
         <is>
@@ -53134,12 +53052,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Weighted average number of outstanding common shares – Basic and diluted</t>
+          <t>Impairment of investment in joint venture (note 12)</t>
         </is>
       </c>
       <c r="D495" t="inlineStr"/>
@@ -53173,17 +53091,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K495" s="5" t="n">
-        <v>73.384404</v>
-      </c>
-      <c r="L495" s="5" t="n">
-        <v>82.864284</v>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M495" s="5" t="n">
-        <v>86.09091600000001</v>
-      </c>
-      <c r="N495" s="5" t="n">
-        <v>86.493313</v>
+        <v>-8.403320000000001</v>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O495" t="inlineStr">
         <is>
@@ -53219,15 +53143,19 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Balance – March 31, 2018 83,368,313 15,064,048 1,000,000 3,532,531 (199,667)</t>
-        </is>
-      </c>
-      <c r="D496" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
           <t>-</t>
@@ -53263,16 +53191,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L496" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L496" s="5" t="n">
+        <v>-1.758714</v>
       </c>
       <c r="M496" s="5" t="n">
-        <v>8.517324</v>
+        <v>-9.763612</v>
       </c>
       <c r="N496" s="5" t="n">
-        <v>-10.879588</v>
+        <v>-1.138192</v>
       </c>
       <c r="O496" t="inlineStr">
         <is>
@@ -53308,19 +53234,15 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Net loss - - - - -</t>
-        </is>
-      </c>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Translation adjustment</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
           <t>-</t>
@@ -53356,16 +53278,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L497" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L497" s="5" t="n">
+        <v>-0.482568</v>
       </c>
       <c r="M497" s="5" t="n">
-        <v>-9.763612</v>
-      </c>
-      <c r="N497" s="5" t="n">
-        <v>-9.763612</v>
+        <v>-0.618499</v>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O497" t="inlineStr">
         <is>
@@ -53401,12 +53323,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Translation adjustment - - - - (618,499)</t>
+          <t>Impairment of investment in joint venture</t>
         </is>
       </c>
       <c r="D498" t="inlineStr"/>
@@ -53451,7 +53373,7 @@
         </is>
       </c>
       <c r="M498" s="5" t="n">
-        <v>-0.618499</v>
+        <v>0.8181659999999999</v>
       </c>
       <c r="N498" t="inlineStr">
         <is>
@@ -53492,15 +53414,19 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Impairment of investment in joint</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Impairment of investment in joint venture - - - - 818,166</t>
-        </is>
-      </c>
-      <c r="D499" t="inlineStr"/>
+          <t>Comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
           <t>-</t>
@@ -53531,23 +53457,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L499" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K499" s="5" t="n">
+        <v>-2.403702</v>
+      </c>
+      <c r="L499" s="5" t="n">
+        <v>-2.241282</v>
       </c>
       <c r="M499" s="5" t="n">
-        <v>0.8181659999999999</v>
-      </c>
-      <c r="N499" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-9.563945</v>
+      </c>
+      <c r="N499" s="5" t="n">
+        <v>-1.138192</v>
       </c>
       <c r="O499" t="inlineStr">
         <is>
@@ -53583,15 +53503,19 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Impairment of investment in joint</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Comprehensive loss 199,667</t>
-        </is>
-      </c>
-      <c r="D500" t="inlineStr"/>
+          <t>Loss per share - Basic and diluted loss per share</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
           <t>-</t>
@@ -53622,21 +53546,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L500" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K500" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="L500" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="M500" s="5" t="n">
-        <v>-9.563945</v>
+        <v>-1.1e-07</v>
       </c>
       <c r="N500" s="5" t="n">
-        <v>-9.763612</v>
+        <v>-1e-08</v>
       </c>
       <c r="O500" t="inlineStr">
         <is>
@@ -53672,12 +53592,12 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Impairment of investment in joint</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Shares issued for cash (note 18) 3,125,000 1,000,000 (1,000,000) - -</t>
+          <t>Weighted average number of outstanding common shares – Basic and diluted</t>
         </is>
       </c>
       <c r="D501" t="inlineStr"/>
@@ -53711,25 +53631,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L501" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M501" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N501" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K501" s="5" t="n">
+        <v>73.384404</v>
+      </c>
+      <c r="L501" s="5" t="n">
+        <v>82.864284</v>
+      </c>
+      <c r="M501" s="5" t="n">
+        <v>86.09091600000001</v>
+      </c>
+      <c r="N501" s="5" t="n">
+        <v>86.493313</v>
       </c>
       <c r="O501" t="inlineStr">
         <is>
@@ -53765,12 +53677,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Fair value allocated to warrants</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>(note 18) - (125,000) - 125,000 -</t>
+          <t>Balance – March 31, 2018 83,368,313 15,064,048 1,000,000 3,532,531 (199,667)</t>
         </is>
       </c>
       <c r="D502" t="inlineStr"/>
@@ -53814,15 +53726,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M502" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N502" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M502" s="5" t="n">
+        <v>8.517324</v>
+      </c>
+      <c r="N502" s="5" t="n">
+        <v>-10.879588</v>
       </c>
       <c r="O502" t="inlineStr">
         <is>
@@ -53858,15 +53766,19 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Fair value allocated to warrants</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Finders fees - 90,861 - - -</t>
-        </is>
-      </c>
-      <c r="D503" t="inlineStr"/>
+          <t>Net loss - - - - -</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
           <t>-</t>
@@ -53908,12 +53820,10 @@
         </is>
       </c>
       <c r="M503" s="5" t="n">
-        <v>0.090861</v>
-      </c>
-      <c r="N503" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-9.763612</v>
+      </c>
+      <c r="N503" s="5" t="n">
+        <v>-9.763612</v>
       </c>
       <c r="O503" t="inlineStr">
         <is>
@@ -53949,12 +53859,12 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Fair value allocated to warrants</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Stock based compensation (note 18) - - - 269,985 -</t>
+          <t>Translation adjustment - - - - (618,499)</t>
         </is>
       </c>
       <c r="D504" t="inlineStr"/>
@@ -53999,7 +53909,7 @@
         </is>
       </c>
       <c r="M504" s="5" t="n">
-        <v>0.269985</v>
+        <v>-0.618499</v>
       </c>
       <c r="N504" t="inlineStr">
         <is>
@@ -54040,12 +53950,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Fair value allocated to warrants</t>
+          <t>Impairment of investment in joint</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Balance – March 31, 2019 86,493,313 16,029,909 - 3,927,516 -</t>
+          <t>Impairment of investment in joint venture - - - - 818,166</t>
         </is>
       </c>
       <c r="D505" t="inlineStr"/>
@@ -54090,10 +54000,12 @@
         </is>
       </c>
       <c r="M505" s="5" t="n">
-        <v>-0.685775</v>
-      </c>
-      <c r="N505" s="5" t="n">
-        <v>-20.6432</v>
+        <v>0.8181659999999999</v>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O505" t="inlineStr">
         <is>
@@ -54129,19 +54041,15 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Fair value allocated to warrants</t>
+          <t>Impairment of investment in joint</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Net loss - - - - -</t>
-        </is>
-      </c>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Comprehensive loss 199,667</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr"/>
       <c r="E506" t="inlineStr">
         <is>
           <t>-</t>
@@ -54183,10 +54091,10 @@
         </is>
       </c>
       <c r="M506" s="5" t="n">
-        <v>-1.138192</v>
+        <v>-9.563945</v>
       </c>
       <c r="N506" s="5" t="n">
-        <v>-1.138192</v>
+        <v>-9.763612</v>
       </c>
       <c r="O506" t="inlineStr">
         <is>
@@ -54222,12 +54130,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Fair value allocated to warrants</t>
+          <t>Impairment of investment in joint</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Balance – March 31, 2020 86,493,313 16,029,909 - 3,927,516 -</t>
+          <t>Shares issued for cash (note 18) 3,125,000 1,000,000 (1,000,000) - -</t>
         </is>
       </c>
       <c r="D507" t="inlineStr"/>
@@ -54271,11 +54179,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M507" s="5" t="n">
-        <v>-1.823967</v>
-      </c>
-      <c r="N507" s="5" t="n">
-        <v>-21.781392</v>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O507" t="inlineStr">
         <is>
@@ -54311,19 +54223,15 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Fair value allocated to warrants</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Depreciation (note 12)</t>
-        </is>
-      </c>
-      <c r="D508" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>(note 18) - (125,000) - 125,000 -</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr"/>
       <c r="E508" t="inlineStr">
         <is>
           <t>-</t>
@@ -54359,11 +54267,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L508" s="5" t="n">
-        <v>0.09596499999999999</v>
-      </c>
-      <c r="M508" s="5" t="n">
-        <v>0.125748</v>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N508" t="inlineStr">
         <is>
@@ -54404,19 +54316,15 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Fair value allocated to warrants</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Management and consulting fees (note 14)</t>
-        </is>
-      </c>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Finders fees - 90,861 - - -</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr"/>
       <c r="E509" t="inlineStr">
         <is>
           <t>-</t>
@@ -54452,11 +54360,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L509" s="5" t="n">
-        <v>0.630987</v>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M509" s="5" t="n">
-        <v>0.456889</v>
+        <v>0.090861</v>
       </c>
       <c r="N509" t="inlineStr">
         <is>
@@ -54497,12 +54407,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Fair value allocated to warrants</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Stock-based compensation (note 17)</t>
+          <t>Stock based compensation (note 18) - - - 269,985 -</t>
         </is>
       </c>
       <c r="D510" t="inlineStr"/>
@@ -54541,8 +54451,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L510" s="5" t="n">
-        <v>0.178789</v>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M510" s="5" t="n">
         <v>0.269985</v>
@@ -54586,19 +54498,15 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Fair value allocated to warrants</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Interest expense</t>
-        </is>
-      </c>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Balance – March 31, 2019 86,493,313 16,029,909 - 3,927,516 -</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr"/>
       <c r="E511" t="inlineStr">
         <is>
           <t>-</t>
@@ -54634,18 +54542,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L511" s="5" t="n">
-        <v>0.008114</v>
-      </c>
-      <c r="M511" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N511" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M511" s="5" t="n">
+        <v>-0.685775</v>
+      </c>
+      <c r="N511" s="5" t="n">
+        <v>-20.6432</v>
       </c>
       <c r="O511" t="inlineStr">
         <is>
@@ -54681,17 +54587,17 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Fair value allocated to warrants</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Net loss - - - - -</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -54729,16 +54635,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L512" s="5" t="n">
-        <v>-0.003918</v>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M512" s="5" t="n">
-        <v>-0.00033</v>
-      </c>
-      <c r="N512" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.138192</v>
+      </c>
+      <c r="N512" s="5" t="n">
+        <v>-1.138192</v>
       </c>
       <c r="O512" t="inlineStr">
         <is>
@@ -54774,12 +54680,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Fair value allocated to warrants</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Share of loss in investment using the equity method (note 13)</t>
+          <t>Balance – March 31, 2020 86,493,313 16,029,909 - 3,927,516 -</t>
         </is>
       </c>
       <c r="D513" t="inlineStr"/>
@@ -54818,16 +54724,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L513" s="5" t="n">
-        <v>0.096133</v>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M513" s="5" t="n">
-        <v>0.000656</v>
-      </c>
-      <c r="N513" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.823967</v>
+      </c>
+      <c r="N513" s="5" t="n">
+        <v>-21.781392</v>
       </c>
       <c r="O513" t="inlineStr">
         <is>
@@ -54863,15 +54769,19 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Write-off of Pathaha Agro deposit (note 10)</t>
-        </is>
-      </c>
-      <c r="D514" t="inlineStr"/>
+          <t>Depreciation (note 12)</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E514" t="inlineStr">
         <is>
           <t>-</t>
@@ -54907,13 +54817,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L514" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L514" s="5" t="n">
+        <v>0.09596499999999999</v>
       </c>
       <c r="M514" s="5" t="n">
-        <v>-0.120267</v>
+        <v>0.125748</v>
       </c>
       <c r="N514" t="inlineStr">
         <is>
@@ -54954,15 +54862,19 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Impairment of investment in joint venture (note 13)</t>
-        </is>
-      </c>
-      <c r="D515" t="inlineStr"/>
+          <t>Management and consulting fees (note 14)</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E515" t="inlineStr">
         <is>
           <t>-</t>
@@ -54998,13 +54910,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L515" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L515" s="5" t="n">
+        <v>0.630987</v>
       </c>
       <c r="M515" s="5" t="n">
-        <v>-8.403320000000001</v>
+        <v>0.456889</v>
       </c>
       <c r="N515" t="inlineStr">
         <is>
@@ -55045,12 +54955,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>(#)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Balance – April 1, 2018 83,368,313 15,064,048 1,000,000 3,532,531 (199,667)</t>
+          <t>Stock-based compensation (note 17)</t>
         </is>
       </c>
       <c r="D516" t="inlineStr"/>
@@ -55090,10 +55000,10 @@
         </is>
       </c>
       <c r="L516" s="5" t="n">
-        <v>8.517324</v>
+        <v>0.178789</v>
       </c>
       <c r="M516" s="5" t="n">
-        <v>-10.879588</v>
+        <v>0.269985</v>
       </c>
       <c r="N516" t="inlineStr">
         <is>
@@ -55134,17 +55044,17 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>(#)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Net loss - - - - -</t>
+          <t>Interest expense</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -55183,10 +55093,12 @@
         </is>
       </c>
       <c r="L517" s="5" t="n">
-        <v>-9.763612</v>
-      </c>
-      <c r="M517" s="5" t="n">
-        <v>-9.763612</v>
+        <v>0.008114</v>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N517" t="inlineStr">
         <is>
@@ -55227,15 +55139,19 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>(#)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Translation adjustment - - - - (618,499)</t>
-        </is>
-      </c>
-      <c r="D518" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E518" t="inlineStr">
         <is>
           <t>-</t>
@@ -55272,12 +55188,10 @@
         </is>
       </c>
       <c r="L518" s="5" t="n">
-        <v>-0.618499</v>
-      </c>
-      <c r="M518" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.003918</v>
+      </c>
+      <c r="M518" s="5" t="n">
+        <v>-0.00033</v>
       </c>
       <c r="N518" t="inlineStr">
         <is>
@@ -55318,12 +55232,12 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>(#)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Impairment of investment in joint venture - - - - 818,166</t>
+          <t>Share of loss in investment using the equity method (note 13)</t>
         </is>
       </c>
       <c r="D519" t="inlineStr"/>
@@ -55363,12 +55277,10 @@
         </is>
       </c>
       <c r="L519" s="5" t="n">
-        <v>0.8181659999999999</v>
-      </c>
-      <c r="M519" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.096133</v>
+      </c>
+      <c r="M519" s="5" t="n">
+        <v>0.000656</v>
       </c>
       <c r="N519" t="inlineStr">
         <is>
@@ -55409,12 +55321,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>(#)</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Comprehensive loss 199,667</t>
+          <t>Write-off of Pathaha Agro deposit (note 10)</t>
         </is>
       </c>
       <c r="D520" t="inlineStr"/>
@@ -55453,11 +55365,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L520" s="5" t="n">
-        <v>-9.563945</v>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M520" s="5" t="n">
-        <v>-9.763612</v>
+        <v>-0.120267</v>
       </c>
       <c r="N520" t="inlineStr">
         <is>
@@ -55498,12 +55412,12 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>(#)</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Shares issued for cash (note 17) 3,125,000 1,000,000 (1,000,000) - -</t>
+          <t>Impairment of investment in joint venture (note 13)</t>
         </is>
       </c>
       <c r="D521" t="inlineStr"/>
@@ -55547,10 +55461,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M521" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M521" s="5" t="n">
+        <v>-8.403320000000001</v>
       </c>
       <c r="N521" t="inlineStr">
         <is>
@@ -55596,7 +55508,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Fair value allocated to warrants (note 17) - (125,000) - 125,000 -</t>
+          <t>Balance – April 1, 2018 83,368,313 15,064,048 1,000,000 3,532,531 (199,667)</t>
         </is>
       </c>
       <c r="D522" t="inlineStr"/>
@@ -55635,15 +55547,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L522" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M522" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L522" s="5" t="n">
+        <v>8.517324</v>
+      </c>
+      <c r="M522" s="5" t="n">
+        <v>-10.879588</v>
       </c>
       <c r="N522" t="inlineStr">
         <is>
@@ -55689,10 +55597,14 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Finders fees - 90,861 - - -</t>
-        </is>
-      </c>
-      <c r="D523" t="inlineStr"/>
+          <t>Net loss - - - - -</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E523" t="inlineStr">
         <is>
           <t>-</t>
@@ -55729,12 +55641,10 @@
         </is>
       </c>
       <c r="L523" s="5" t="n">
-        <v>0.090861</v>
-      </c>
-      <c r="M523" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-9.763612</v>
+      </c>
+      <c r="M523" s="5" t="n">
+        <v>-9.763612</v>
       </c>
       <c r="N523" t="inlineStr">
         <is>
@@ -55780,7 +55690,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Stock based compensation (note 17) - - - 269,985 -</t>
+          <t>Translation adjustment - - - - (618,499)</t>
         </is>
       </c>
       <c r="D524" t="inlineStr"/>
@@ -55820,7 +55730,7 @@
         </is>
       </c>
       <c r="L524" s="5" t="n">
-        <v>0.269985</v>
+        <v>-0.618499</v>
       </c>
       <c r="M524" t="inlineStr">
         <is>
@@ -55871,7 +55781,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Balance- March 31, 2019 86,493,313 16,029,909 - 3,927,516 -</t>
+          <t>Impairment of investment in joint venture - - - - 818,166</t>
         </is>
       </c>
       <c r="D525" t="inlineStr"/>
@@ -55911,10 +55821,12 @@
         </is>
       </c>
       <c r="L525" s="5" t="n">
-        <v>-0.685775</v>
-      </c>
-      <c r="M525" s="5" t="n">
-        <v>-20.6432</v>
+        <v>0.8181659999999999</v>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N525" t="inlineStr">
         <is>
@@ -55960,7 +55872,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Balance – April 1, 2017 82,783,127 14,775,731 - 3,455,096 282,901</t>
+          <t>Comprehensive loss 199,667</t>
         </is>
       </c>
       <c r="D526" t="inlineStr"/>
@@ -56000,10 +55912,10 @@
         </is>
       </c>
       <c r="L526" s="5" t="n">
-        <v>9.392854</v>
+        <v>-9.563945</v>
       </c>
       <c r="M526" s="5" t="n">
-        <v>-9.120874000000001</v>
+        <v>-9.763612</v>
       </c>
       <c r="N526" t="inlineStr">
         <is>
@@ -56049,7 +55961,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Translation adjustment - - - - (482,568)</t>
+          <t>Shares issued for cash (note 17) 3,125,000 1,000,000 (1,000,000) - -</t>
         </is>
       </c>
       <c r="D527" t="inlineStr"/>
@@ -56088,8 +56000,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L527" s="5" t="n">
-        <v>-0.482568</v>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M527" t="inlineStr">
         <is>
@@ -56140,7 +56054,7 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Comprehensive loss - - - - (482,568)</t>
+          <t>Fair value allocated to warrants (note 17) - (125,000) - 125,000 -</t>
         </is>
       </c>
       <c r="D528" t="inlineStr"/>
@@ -56179,11 +56093,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L528" s="5" t="n">
-        <v>-2.241282</v>
-      </c>
-      <c r="M528" s="5" t="n">
-        <v>-1.758714</v>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N528" t="inlineStr">
         <is>
@@ -56229,7 +56147,7 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Subscription received in advance (note 17) - - 1,000,000 - -</t>
+          <t>Finders fees - 90,861 - - -</t>
         </is>
       </c>
       <c r="D529" t="inlineStr"/>
@@ -56269,7 +56187,7 @@
         </is>
       </c>
       <c r="L529" s="5" t="n">
-        <v>1</v>
+        <v>0.090861</v>
       </c>
       <c r="M529" t="inlineStr">
         <is>
@@ -56320,7 +56238,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Stock based compensation (note 17) - - - 178,789 -</t>
+          <t>Stock based compensation (note 17) - - - 269,985 -</t>
         </is>
       </c>
       <c r="D530" t="inlineStr"/>
@@ -56360,7 +56278,7 @@
         </is>
       </c>
       <c r="L530" s="5" t="n">
-        <v>0.178789</v>
+        <v>0.269985</v>
       </c>
       <c r="M530" t="inlineStr">
         <is>
@@ -56411,7 +56329,7 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Options exercised (note 17) 400,000 225,354 - (101,354) -</t>
+          <t>Balance- March 31, 2019 86,493,313 16,029,909 - 3,927,516 -</t>
         </is>
       </c>
       <c r="D531" t="inlineStr"/>
@@ -56451,12 +56369,10 @@
         </is>
       </c>
       <c r="L531" s="5" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="M531" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.685775</v>
+      </c>
+      <c r="M531" s="5" t="n">
+        <v>-20.6432</v>
       </c>
       <c r="N531" t="inlineStr">
         <is>
@@ -56502,7 +56418,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Warrant exercised (note 17) 185,186 62,963 - - -</t>
+          <t>Balance – April 1, 2017 82,783,127 14,775,731 - 3,455,096 282,901</t>
         </is>
       </c>
       <c r="D532" t="inlineStr"/>
@@ -56542,12 +56458,10 @@
         </is>
       </c>
       <c r="L532" s="5" t="n">
-        <v>0.06296300000000001</v>
-      </c>
-      <c r="M532" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.392854</v>
+      </c>
+      <c r="M532" s="5" t="n">
+        <v>-9.120874000000001</v>
       </c>
       <c r="N532" t="inlineStr">
         <is>
@@ -56593,7 +56507,7 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Balance – March 31, 2018 83,368,313 15,064,048 1,000,000 3,532,531 (199,667)</t>
+          <t>Translation adjustment - - - - (482,568)</t>
         </is>
       </c>
       <c r="D533" t="inlineStr"/>
@@ -56633,10 +56547,12 @@
         </is>
       </c>
       <c r="L533" s="5" t="n">
-        <v>8.517324</v>
-      </c>
-      <c r="M533" s="5" t="n">
-        <v>-10.879588</v>
+        <v>-0.482568</v>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N533" t="inlineStr">
         <is>
@@ -56677,12 +56593,12 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Expenses (Income)</t>
+          <t>(#)</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Research and development, net of government grants and assistance (note 15)</t>
+          <t>Comprehensive loss - - - - (482,568)</t>
         </is>
       </c>
       <c r="D534" t="inlineStr"/>
@@ -56716,16 +56632,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K534" s="5" t="n">
-        <v>0.758565</v>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L534" s="5" t="n">
-        <v>0.238085</v>
-      </c>
-      <c r="M534" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.241282</v>
+      </c>
+      <c r="M534" s="5" t="n">
+        <v>-1.758714</v>
       </c>
       <c r="N534" t="inlineStr">
         <is>
@@ -56766,19 +56682,15 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Expenses (Income)</t>
+          <t>(#)</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Subscription received in advance (note 17) - - 1,000,000 - -</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr"/>
       <c r="E535" t="inlineStr">
         <is>
           <t>-</t>
@@ -56809,11 +56721,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K535" s="5" t="n">
-        <v>0.045158</v>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L535" s="5" t="n">
-        <v>0.215862</v>
+        <v>1</v>
       </c>
       <c r="M535" t="inlineStr">
         <is>
@@ -56859,19 +56773,15 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Expenses (Income)</t>
+          <t>(#)</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
-        </is>
-      </c>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Stock based compensation (note 17) - - - 178,789 -</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr">
         <is>
           <t>-</t>
@@ -56902,11 +56812,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K536" s="5" t="n">
-        <v>0.13477</v>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L536" s="5" t="n">
-        <v>0.067606</v>
+        <v>0.178789</v>
       </c>
       <c r="M536" t="inlineStr">
         <is>
@@ -56952,12 +56864,12 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Expenses (Income)</t>
+          <t>(#)</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Depreciation expense (note 12)</t>
+          <t>Options exercised (note 17) 400,000 225,354 - (101,354) -</t>
         </is>
       </c>
       <c r="D537" t="inlineStr"/>
@@ -56991,11 +56903,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K537" s="5" t="n">
-        <v>0.055242</v>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L537" s="5" t="n">
-        <v>0.09596499999999999</v>
+        <v>0.124</v>
       </c>
       <c r="M537" t="inlineStr">
         <is>
@@ -57041,19 +56955,15 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Expenses (Income)</t>
+          <t>(#)</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Management and consulting fees (note 14)</t>
-        </is>
-      </c>
-      <c r="D538" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Warrant exercised (note 17) 185,186 62,963 - - -</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr"/>
       <c r="E538" t="inlineStr">
         <is>
           <t>-</t>
@@ -57084,11 +56994,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K538" s="5" t="n">
-        <v>0.8383080000000001</v>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L538" s="5" t="n">
-        <v>0.630987</v>
+        <v>0.06296300000000001</v>
       </c>
       <c r="M538" t="inlineStr">
         <is>
@@ -57134,12 +57046,12 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Expenses (Income)</t>
+          <t>(#)</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Transfer, filing and listing fees</t>
+          <t>Balance – March 31, 2018 83,368,313 15,064,048 1,000,000 3,532,531 (199,667)</t>
         </is>
       </c>
       <c r="D539" t="inlineStr"/>
@@ -57173,16 +57085,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K539" s="5" t="n">
-        <v>0.060298</v>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L539" s="5" t="n">
-        <v>0.05473</v>
-      </c>
-      <c r="M539" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.517324</v>
+      </c>
+      <c r="M539" s="5" t="n">
+        <v>-10.879588</v>
       </c>
       <c r="N539" t="inlineStr">
         <is>
@@ -57228,7 +57140,7 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Investor relations expense</t>
+          <t>Research and development, net of government grants and assistance (note 15)</t>
         </is>
       </c>
       <c r="D540" t="inlineStr"/>
@@ -57263,10 +57175,10 @@
         </is>
       </c>
       <c r="K540" s="5" t="n">
-        <v>0.042809</v>
+        <v>0.758565</v>
       </c>
       <c r="L540" s="5" t="n">
-        <v>0.093038</v>
+        <v>0.238085</v>
       </c>
       <c r="M540" t="inlineStr">
         <is>
@@ -57317,10 +57229,14 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Stock-based compensation (note 17)</t>
-        </is>
-      </c>
-      <c r="D541" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E541" t="inlineStr">
         <is>
           <t>-</t>
@@ -57352,10 +57268,10 @@
         </is>
       </c>
       <c r="K541" s="5" t="n">
-        <v>0.06815400000000001</v>
+        <v>0.045158</v>
       </c>
       <c r="L541" s="5" t="n">
-        <v>0.178789</v>
+        <v>0.215862</v>
       </c>
       <c r="M541" t="inlineStr">
         <is>
@@ -57406,12 +57322,12 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Interest expense</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -57445,10 +57361,10 @@
         </is>
       </c>
       <c r="K542" s="5" t="n">
-        <v>0.00051</v>
+        <v>0.13477</v>
       </c>
       <c r="L542" s="5" t="n">
-        <v>0.008114</v>
+        <v>0.067606</v>
       </c>
       <c r="M542" t="inlineStr">
         <is>
@@ -57499,14 +57415,10 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D543" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Depreciation expense (note 12)</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr"/>
       <c r="E543" t="inlineStr">
         <is>
           <t>-</t>
@@ -57538,10 +57450,10 @@
         </is>
       </c>
       <c r="K543" s="5" t="n">
-        <v>-0.001254</v>
+        <v>0.055242</v>
       </c>
       <c r="L543" s="5" t="n">
-        <v>-0.003918</v>
+        <v>0.09596499999999999</v>
       </c>
       <c r="M543" t="inlineStr">
         <is>
@@ -57592,10 +57504,14 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Accreted Interest (note 15)</t>
-        </is>
-      </c>
-      <c r="D544" t="inlineStr"/>
+          <t>Management and consulting fees (note 14)</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E544" t="inlineStr">
         <is>
           <t>-</t>
@@ -57627,10 +57543,10 @@
         </is>
       </c>
       <c r="K544" s="5" t="n">
-        <v>0.023146</v>
+        <v>0.8383080000000001</v>
       </c>
       <c r="L544" s="5" t="n">
-        <v>0.040494</v>
+        <v>0.630987</v>
       </c>
       <c r="M544" t="inlineStr">
         <is>
@@ -57681,7 +57597,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Realized &amp; unrealized gain on marketable securities</t>
+          <t>Transfer, filing and listing fees</t>
         </is>
       </c>
       <c r="D545" t="inlineStr"/>
@@ -57716,10 +57632,10 @@
         </is>
       </c>
       <c r="K545" s="5" t="n">
-        <v>-0.028122</v>
+        <v>0.060298</v>
       </c>
       <c r="L545" s="5" t="n">
-        <v>-0.002483</v>
+        <v>0.05473</v>
       </c>
       <c r="M545" t="inlineStr">
         <is>
@@ -57770,7 +57686,7 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Share of loss in investments using the equity method (note 13)</t>
+          <t>Investor relations expense</t>
         </is>
       </c>
       <c r="D546" t="inlineStr"/>
@@ -57805,10 +57721,10 @@
         </is>
       </c>
       <c r="K546" s="5" t="n">
-        <v>0.291564</v>
+        <v>0.042809</v>
       </c>
       <c r="L546" s="5" t="n">
-        <v>0.096133</v>
+        <v>0.093038</v>
       </c>
       <c r="M546" t="inlineStr">
         <is>
@@ -57859,14 +57775,10 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Loss on foreign exchange</t>
-        </is>
-      </c>
-      <c r="D547" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Stock-based compensation (note 17)</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr"/>
       <c r="E547" t="inlineStr">
         <is>
           <t>-</t>
@@ -57898,10 +57810,10 @@
         </is>
       </c>
       <c r="K547" s="5" t="n">
-        <v>0.008921999999999999</v>
+        <v>0.06815400000000001</v>
       </c>
       <c r="L547" s="5" t="n">
-        <v>0.045312</v>
+        <v>0.178789</v>
       </c>
       <c r="M547" t="inlineStr">
         <is>
@@ -57952,12 +57864,12 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
+          <t>Interest expense</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -57991,10 +57903,10 @@
         </is>
       </c>
       <c r="K548" s="5" t="n">
-        <v>-2.29807</v>
+        <v>0.00051</v>
       </c>
       <c r="L548" s="5" t="n">
-        <v>-1.758714</v>
+        <v>0.008114</v>
       </c>
       <c r="M548" t="inlineStr">
         <is>
@@ -58040,15 +57952,19 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Expenses (Income)</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Annual translation adjustment</t>
-        </is>
-      </c>
-      <c r="D549" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E549" t="inlineStr">
         <is>
           <t>-</t>
@@ -58080,10 +57996,10 @@
         </is>
       </c>
       <c r="K549" s="5" t="n">
-        <v>-0.105632</v>
+        <v>-0.001254</v>
       </c>
       <c r="L549" s="5" t="n">
-        <v>-0.482568</v>
+        <v>-0.003918</v>
       </c>
       <c r="M549" t="inlineStr">
         <is>
@@ -58129,12 +58045,12 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>-See Accompanying Notes-</t>
+          <t>Expenses (Income)</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Total shareholders'equity ($) 9,392,854 (1,758,714) (482,568) (2,241,282) 1,000,000 178,789 124,000 62,963 8,517,324 8,007,956 (2,298,070) (105,632) (2,403,702) 68,154 3,583,606 (144,593)</t>
+          <t>Accreted Interest (note 15)</t>
         </is>
       </c>
       <c r="D550" t="inlineStr"/>
@@ -58169,10 +58085,10 @@
         </is>
       </c>
       <c r="K550" s="5" t="n">
-        <v>9.392854</v>
+        <v>0.023146</v>
       </c>
       <c r="L550" s="5" t="n">
-        <v>0.281433</v>
+        <v>0.040494</v>
       </c>
       <c r="M550" t="inlineStr">
         <is>
@@ -58218,12 +58134,12 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>-See Accompanying Notes-</t>
+          <t>Expenses (Income)</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Deficit ($) (9,120,874) (1,758,714) - (1,758,714) - - - - (10,879,588) (6,822,804) (2,298,070) - (2,298,070) - - -</t>
+          <t>Realized &amp; unrealized gain on marketable securities</t>
         </is>
       </c>
       <c r="D551" t="inlineStr"/>
@@ -58258,12 +58174,10 @@
         </is>
       </c>
       <c r="K551" s="5" t="n">
-        <v>-9.120874000000001</v>
-      </c>
-      <c r="L551" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.028122</v>
+      </c>
+      <c r="L551" s="5" t="n">
+        <v>-0.002483</v>
       </c>
       <c r="M551" t="inlineStr">
         <is>
@@ -58309,12 +58223,12 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>-See Accompanying Notes-</t>
+          <t>Expenses (Income)</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Accumulated other Comprehensiveincome ($) 282,901 - (482,568) (482,568) - - - - (199,667) 388,533 - (105,632) (105,632) - - -</t>
+          <t>Share of loss in investments using the equity method (note 13)</t>
         </is>
       </c>
       <c r="D552" t="inlineStr"/>
@@ -58349,12 +58263,10 @@
         </is>
       </c>
       <c r="K552" s="5" t="n">
-        <v>0.282901</v>
-      </c>
-      <c r="L552" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.291564</v>
+      </c>
+      <c r="L552" s="5" t="n">
+        <v>0.096133</v>
       </c>
       <c r="M552" t="inlineStr">
         <is>
@@ -58398,13 +58310,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B553" t="inlineStr"/>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Expenses (Income)</t>
+        </is>
+      </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS’ ShareCapital ($) 14,775,731 -- -- -- -- -- 225,354 62,963 15,064,048 11,067,378 -- -- -- -- 3,536,931 (144,593)-</t>
-        </is>
-      </c>
-      <c r="D553" t="inlineStr"/>
+          <t>Loss on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E553" t="inlineStr">
         <is>
           <t>-</t>
@@ -58436,10 +58356,10 @@
         </is>
       </c>
       <c r="K553" s="5" t="n">
-        <v>14.775731</v>
+        <v>0.008921999999999999</v>
       </c>
       <c r="L553" s="5" t="n">
-        <v>0.316015</v>
+        <v>0.045312</v>
       </c>
       <c r="M553" t="inlineStr">
         <is>
@@ -58483,13 +58403,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B554" t="inlineStr"/>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Expenses (Income)</t>
+        </is>
+      </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>2017 March</t>
-        </is>
-      </c>
-      <c r="D554" t="inlineStr"/>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E554" t="inlineStr">
         <is>
           <t>-</t>
@@ -58515,16 +58443,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J554" s="5" t="n">
-        <v>0.002016</v>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K554" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="L554" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.29807</v>
+      </c>
+      <c r="L554" s="5" t="n">
+        <v>-1.758714</v>
       </c>
       <c r="M554" t="inlineStr">
         <is>
@@ -58570,12 +58498,12 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>(105,632)</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year (2,403,702) Annual translation adjustment</t>
+          <t>Annual translation adjustment</t>
         </is>
       </c>
       <c r="D555" t="inlineStr"/>
@@ -58604,16 +58532,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J555" s="5" t="n">
-        <v>-3.53505</v>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K555" s="5" t="n">
-        <v>-0.531317</v>
-      </c>
-      <c r="L555" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.105632</v>
+      </c>
+      <c r="L555" s="5" t="n">
+        <v>-0.482568</v>
       </c>
       <c r="M555" t="inlineStr">
         <is>
@@ -58664,7 +58592,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>AS AT MARCH 31, 2017 AND MARCH</t>
+          <t>Total shareholders'equity ($) 9,392,854 (1,758,714) (482,568) (2,241,282) 1,000,000 178,789 124,000 62,963 8,517,324 8,007,956 (2,298,070) (105,632) (2,403,702) 68,154 3,583,606 (144,593)</t>
         </is>
       </c>
       <c r="D556" t="inlineStr"/>
@@ -58693,16 +58621,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J556" s="5" t="n">
-        <v>0.002016</v>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K556" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="L556" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.392854</v>
+      </c>
+      <c r="L556" s="5" t="n">
+        <v>0.281433</v>
       </c>
       <c r="M556" t="inlineStr">
         <is>
@@ -58748,12 +58676,12 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>(#)            ($)               ($)                  ($)             ($)                ($)</t>
+          <t>-See Accompanying Notes-</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Balance - March 31, 2016 69,347,967 11,067,378 3,374,849 388,533</t>
+          <t>Deficit ($) (9,120,874) (1,758,714) - (1,758,714) - - - - (10,879,588) (6,822,804) (2,298,070) - (2,298,070) - - -</t>
         </is>
       </c>
       <c r="D557" t="inlineStr"/>
@@ -58782,11 +58710,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J557" s="5" t="n">
-        <v>8.007956</v>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K557" s="5" t="n">
-        <v>-6.822804</v>
+        <v>-9.120874000000001</v>
       </c>
       <c r="L557" t="inlineStr">
         <is>
@@ -58837,12 +58767,12 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>(#)            ($)               ($)                  ($)             ($)                ($)</t>
+          <t>-See Accompanying Notes-</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>(#)            ($)               ($)                  ($)             ($)                ($) total</t>
+          <t>Accumulated other Comprehensiveincome ($) 282,901 - (482,568) (482,568) - - - - (199,667) 388,533 - (105,632) (105,632) - - -</t>
         </is>
       </c>
       <c r="D558" t="inlineStr"/>
@@ -58871,11 +58801,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J558" s="5" t="n">
-        <v>-2.29807</v>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K558" s="5" t="n">
-        <v>-2.29807</v>
+        <v>0.282901</v>
       </c>
       <c r="L558" t="inlineStr">
         <is>
@@ -58924,14 +58856,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B559" t="inlineStr">
-        <is>
-          <t>-                     -                        -          (105,632)    (2,298,070)       (2,403,702)ComprehensiveAnnual translationlossadjustment</t>
-        </is>
-      </c>
+      <c r="B559" t="inlineStr"/>
       <c r="C559" t="inlineStr">
         <is>
-          <t>- - 68,154 - - 68,154 Stock based compensation (note 17) 12,197,103 3,536,931 46,675 - - 3,583,606 Shares issued for cash (note 17) - (144,593) - -</t>
+          <t>SHAREHOLDERS’ ShareCapital ($) 14,775,731 -- -- -- -- -- 225,354 62,963 15,064,048 11,067,378 -- -- -- -- 3,536,931 (144,593)-</t>
         </is>
       </c>
       <c r="D559" t="inlineStr"/>
@@ -58960,18 +58888,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J559" s="5" t="n">
-        <v>-0.144593</v>
-      </c>
-      <c r="K559" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L559" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K559" s="5" t="n">
+        <v>14.775731</v>
+      </c>
+      <c r="L559" s="5" t="n">
+        <v>0.316015</v>
       </c>
       <c r="M559" t="inlineStr">
         <is>
@@ -59015,14 +58941,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B560" t="inlineStr">
-        <is>
-          <t>82,783,127    14,775,731       3,455,096           282,901    (9,120,874)         9,392,854BalanceWarrants–exercisedMarch 31,(note201717)</t>
-        </is>
-      </c>
+      <c r="B560" t="inlineStr"/>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Balance - March 31, 2015 42,553,633 7,173,780 2,514,921 919,850</t>
+          <t>2017 March</t>
         </is>
       </c>
       <c r="D560" t="inlineStr"/>
@@ -59052,10 +58974,10 @@
         </is>
       </c>
       <c r="J560" s="5" t="n">
-        <v>6.78948</v>
+        <v>0.002016</v>
       </c>
       <c r="K560" s="5" t="n">
-        <v>-3.819071</v>
+        <v>3.1e-05</v>
       </c>
       <c r="L560" t="inlineStr">
         <is>
@@ -59106,12 +59028,12 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>82,783,127    14,775,731       3,455,096           282,901    (9,120,874)         9,392,854BalanceWarrants–exercisedMarch 31,(note201717)</t>
+          <t>(105,632)</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>82,783,127    14,775,731       3,455,096           282,901    (9,120,874)         9,392,854BalanceWarrants–exercisedMarch 31,(note201717) total</t>
+          <t>Comprehensive loss for the year (2,403,702) Annual translation adjustment</t>
         </is>
       </c>
       <c r="D561" t="inlineStr"/>
@@ -59141,10 +59063,10 @@
         </is>
       </c>
       <c r="J561" s="5" t="n">
-        <v>-3.003733</v>
+        <v>-3.53505</v>
       </c>
       <c r="K561" s="5" t="n">
-        <v>-3.003733</v>
+        <v>-0.531317</v>
       </c>
       <c r="L561" t="inlineStr">
         <is>
@@ -59195,12 +59117,12 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>82,783,127    14,775,731       3,455,096           282,901    (9,120,874)         9,392,854BalanceWarrants–exercisedMarch 31,(note201717)</t>
+          <t>-See Accompanying Notes-</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Comprehensive lossAnnual translation adjustment - - - (531,317)</t>
+          <t>AS AT MARCH 31, 2017 AND MARCH</t>
         </is>
       </c>
       <c r="D562" t="inlineStr"/>
@@ -59230,10 +59152,10 @@
         </is>
       </c>
       <c r="J562" s="5" t="n">
-        <v>-3.53505</v>
+        <v>0.002016</v>
       </c>
       <c r="K562" s="5" t="n">
-        <v>-3.003733</v>
+        <v>3.1e-05</v>
       </c>
       <c r="L562" t="inlineStr">
         <is>
@@ -59284,12 +59206,12 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>82,783,127    14,775,731       3,455,096           282,901    (9,120,874)         9,392,854BalanceWarrants–exercisedMarch 31,(note201717)</t>
+          <t>(#)            ($)               ($)                  ($)             ($)                ($)</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>- - 837,157 - - 837,157 Stock based compensation (note 17) 20,906,001 2,926,840 - - - 2,926,840 Shares issued for cash (note 17) - (63,053) 34,582 - - (28,471) Share issuance costs (note 17) 80,000 23,811</t>
+          <t>Balance - March 31, 2016 69,347,967 11,067,378 3,374,849 388,533</t>
         </is>
       </c>
       <c r="D563" t="inlineStr"/>
@@ -59319,10 +59241,10 @@
         </is>
       </c>
       <c r="J563" s="5" t="n">
-        <v>0.012</v>
+        <v>8.007956</v>
       </c>
       <c r="K563" s="5" t="n">
-        <v>-0.011811</v>
+        <v>-6.822804</v>
       </c>
       <c r="L563" t="inlineStr">
         <is>
@@ -59373,12 +59295,12 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>(531,317)</t>
+          <t>(#)            ($)               ($)                  ($)             ($)                ($)</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year (3,535,050) Annual translation adjustment</t>
+          <t>(#)            ($)               ($)                  ($)             ($)                ($) total</t>
         </is>
       </c>
       <c r="D564" t="inlineStr"/>
@@ -59402,16 +59324,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I564" s="5" t="n">
-        <v>-1.352997</v>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J564" s="5" t="n">
-        <v>0.9198499999999999</v>
-      </c>
-      <c r="K564" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.29807</v>
+      </c>
+      <c r="K564" s="5" t="n">
+        <v>-2.29807</v>
       </c>
       <c r="L564" t="inlineStr">
         <is>
@@ -59462,12 +59384,12 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>(#)            ($)              ($)                  ($)             ($)                ($)</t>
+          <t>-                     -                        -          (105,632)    (2,298,070)       (2,403,702)ComprehensiveAnnual translationlossadjustment</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Balance - March 31, 2015 42,553,633 7,173,780 2,514,921 919,850</t>
+          <t>- - 68,154 - - 68,154 Stock based compensation (note 17) 12,197,103 3,536,931 46,675 - - 3,583,606 Shares issued for cash (note 17) - (144,593) - -</t>
         </is>
       </c>
       <c r="D565" t="inlineStr"/>
@@ -59491,11 +59413,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I565" s="5" t="n">
-        <v>6.78948</v>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J565" s="5" t="n">
-        <v>-3.819071</v>
+        <v>-0.144593</v>
       </c>
       <c r="K565" t="inlineStr">
         <is>
@@ -59551,12 +59475,12 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>(#)            ($)              ($)                  ($)             ($)                ($)</t>
+          <t>82,783,127    14,775,731       3,455,096           282,901    (9,120,874)         9,392,854BalanceWarrants–exercisedMarch 31,(note201717)</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>(#)            ($)              ($)                  ($)             ($)                ($) total</t>
+          <t>Balance - March 31, 2015 42,553,633 7,173,780 2,514,921 919,850</t>
         </is>
       </c>
       <c r="D566" t="inlineStr"/>
@@ -59580,16 +59504,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I566" s="5" t="n">
-        <v>-3.003733</v>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J566" s="5" t="n">
-        <v>-3.003733</v>
-      </c>
-      <c r="K566" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.78948</v>
+      </c>
+      <c r="K566" s="5" t="n">
+        <v>-3.819071</v>
       </c>
       <c r="L566" t="inlineStr">
         <is>
@@ -59640,12 +59564,12 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>(#)            ($)              ($)                  ($)             ($)                ($)</t>
+          <t>82,783,127    14,775,731       3,455,096           282,901    (9,120,874)         9,392,854BalanceWarrants–exercisedMarch 31,(note201717)</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Comprehensive lossAnnual translation adjustment - - - (531,317)</t>
+          <t>82,783,127    14,775,731       3,455,096           282,901    (9,120,874)         9,392,854BalanceWarrants–exercisedMarch 31,(note201717) total</t>
         </is>
       </c>
       <c r="D567" t="inlineStr"/>
@@ -59669,16 +59593,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I567" s="5" t="n">
-        <v>-3.53505</v>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J567" s="5" t="n">
         <v>-3.003733</v>
       </c>
-      <c r="K567" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K567" s="5" t="n">
+        <v>-3.003733</v>
       </c>
       <c r="L567" t="inlineStr">
         <is>
@@ -59729,12 +59653,12 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>(#)            ($)              ($)                  ($)             ($)                ($)</t>
+          <t>82,783,127    14,775,731       3,455,096           282,901    (9,120,874)         9,392,854BalanceWarrants–exercisedMarch 31,(note201717)</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>- - 837,157 - - 837,157 Stock based compensation 20,906,001 2,926,840 - - - 2,926,840 Shares issued for cash - (63,053) 34,582 - - (28,471) Share issuance costs 80,000 23,811 (11,811) -</t>
+          <t>Comprehensive lossAnnual translation adjustment - - - (531,317)</t>
         </is>
       </c>
       <c r="D568" t="inlineStr"/>
@@ -59758,18 +59682,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I568" s="5" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="J568" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K568" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J568" s="5" t="n">
+        <v>-3.53505</v>
+      </c>
+      <c r="K568" s="5" t="n">
+        <v>-3.003733</v>
       </c>
       <c r="L568" t="inlineStr">
         <is>
@@ -59820,12 +59742,12 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>(#)            ($)              ($)                  ($)             ($)                ($)</t>
+          <t>82,783,127    14,775,731       3,455,096           282,901    (9,120,874)         9,392,854BalanceWarrants–exercisedMarch 31,(note201717)</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>69,347,967 11,067,378 3,374,849 388,533 (6,822,804) 8,007,956BalanceWarrants–exercisedMarch</t>
+          <t>- - 837,157 - - 837,157 Stock based compensation (note 17) 20,906,001 2,926,840 - - - 2,926,840 Shares issued for cash (note 17) - (63,053) 34,582 - - (28,471) Share issuance costs (note 17) 80,000 23,811</t>
         </is>
       </c>
       <c r="D569" t="inlineStr"/>
@@ -59849,16 +59771,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I569" s="5" t="n">
-        <v>0.002016</v>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J569" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="K569" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.012</v>
+      </c>
+      <c r="K569" s="5" t="n">
+        <v>-0.011811</v>
       </c>
       <c r="L569" t="inlineStr">
         <is>
@@ -59909,12 +59831,12 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>(531,317)</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Balance - March 31, 2014 22,453,163 1,989,416 131,034 -</t>
+          <t>Comprehensive loss for the year (3,535,050) Annual translation adjustment</t>
         </is>
       </c>
       <c r="D570" t="inlineStr"/>
@@ -59939,10 +59861,10 @@
         </is>
       </c>
       <c r="I570" s="5" t="n">
-        <v>0.574226</v>
+        <v>-1.352997</v>
       </c>
       <c r="J570" s="5" t="n">
-        <v>-1.546224</v>
+        <v>0.9198499999999999</v>
       </c>
       <c r="K570" t="inlineStr">
         <is>
@@ -59998,12 +59920,12 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>(#)            ($)              ($)                  ($)             ($)                ($)</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>- total</t>
+          <t>Balance - March 31, 2015 42,553,633 7,173,780 2,514,921 919,850</t>
         </is>
       </c>
       <c r="D571" t="inlineStr"/>
@@ -60028,10 +59950,10 @@
         </is>
       </c>
       <c r="I571" s="5" t="n">
-        <v>-2.272847</v>
+        <v>6.78948</v>
       </c>
       <c r="J571" s="5" t="n">
-        <v>-2.272847</v>
+        <v>-3.819071</v>
       </c>
       <c r="K571" t="inlineStr">
         <is>
@@ -60087,12 +60009,12 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>(#)            ($)              ($)                  ($)             ($)                ($)</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Comprehensive (income) loss                                            -                     -                       -           919,850    (2,272,847)       (1,352,997)Annual translation adjustment</t>
+          <t>(#)            ($)              ($)                  ($)             ($)                ($) total</t>
         </is>
       </c>
       <c r="D572" t="inlineStr"/>
@@ -60117,12 +60039,10 @@
         </is>
       </c>
       <c r="I572" s="5" t="n">
-        <v>0.02399</v>
-      </c>
-      <c r="J572" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.003733</v>
+      </c>
+      <c r="J572" s="5" t="n">
+        <v>-3.003733</v>
       </c>
       <c r="K572" t="inlineStr">
         <is>
@@ -60176,10 +60096,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B573" t="inlineStr"/>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>(#)            ($)              ($)                  ($)             ($)                ($)</t>
+        </is>
+      </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>2015 $ March 31,</t>
+          <t>Comprehensive lossAnnual translation adjustment - - - (531,317)</t>
         </is>
       </c>
       <c r="D573" t="inlineStr"/>
@@ -60198,16 +60122,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H573" s="5" t="n">
-        <v>0.05315</v>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I573" s="5" t="n">
-        <v>0.002014</v>
-      </c>
-      <c r="J573" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.53505</v>
+      </c>
+      <c r="J573" s="5" t="n">
+        <v>-3.003733</v>
       </c>
       <c r="K573" t="inlineStr">
         <is>
@@ -60263,12 +60187,12 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>328,193  Stock-based compensation                                                                             23,991</t>
+          <t>(#)            ($)              ($)                  ($)             ($)                ($)</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>435,404 Share of loss in joint venture (note</t>
+          <t>- - 837,157 - - 837,157 Stock based compensation 20,906,001 2,926,840 - - - 2,926,840 Shares issued for cash - (63,053) 34,582 - - (28,471) Share issuance costs 80,000 23,811 (11,811) -</t>
         </is>
       </c>
       <c r="D574" t="inlineStr"/>
@@ -60293,7 +60217,7 @@
         </is>
       </c>
       <c r="I574" s="5" t="n">
-        <v>1.1e-05</v>
+        <v>0.012</v>
       </c>
       <c r="J574" t="inlineStr">
         <is>
@@ -60354,12 +60278,12 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>328,193  Stock-based compensation                                                                             23,991</t>
+          <t>(#)            ($)              ($)                  ($)             ($)                ($)</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>(13,645) Write –down of exploration &amp; evaluation assets (note</t>
+          <t>69,347,967 11,067,378 3,374,849 388,533 (6,822,804) 8,007,956BalanceWarrants–exercisedMarch</t>
         </is>
       </c>
       <c r="D575" t="inlineStr"/>
@@ -60384,12 +60308,10 @@
         </is>
       </c>
       <c r="I575" s="5" t="n">
-        <v>1.2e-05</v>
-      </c>
-      <c r="J575" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002016</v>
+      </c>
+      <c r="J575" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="K575" t="inlineStr">
         <is>
@@ -60445,12 +60367,12 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Loss before income taxes                                                      (2,284,097)  Interest income                                                                                         (334)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>(note 13)</t>
+          <t>Balance - March 31, 2014 22,453,163 1,989,416 131,034 -</t>
         </is>
       </c>
       <c r="D576" t="inlineStr"/>
@@ -60469,16 +60391,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H576" s="5" t="n">
-        <v>-1.105781</v>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I576" s="5" t="n">
-        <v>0.01125</v>
-      </c>
-      <c r="J576" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.574226</v>
+      </c>
+      <c r="J576" s="5" t="n">
+        <v>-1.546224</v>
       </c>
       <c r="K576" t="inlineStr">
         <is>
@@ -60534,12 +60456,12 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>919,850</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year (1,352,997) Cumulative translation adjustment</t>
+          <t>- total</t>
         </is>
       </c>
       <c r="D577" t="inlineStr"/>
@@ -60558,18 +60480,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H577" s="5" t="n">
-        <v>-1.080781</v>
-      </c>
-      <c r="I577" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J577" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I577" s="5" t="n">
+        <v>-2.272847</v>
+      </c>
+      <c r="J577" s="5" t="n">
+        <v>-2.272847</v>
       </c>
       <c r="K577" t="inlineStr">
         <is>
@@ -60625,12 +60545,12 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>(#)            $               $                 $                 ($)               ($)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Balance - March 31, 2014 22,453,163 1,989,416 131,034 -</t>
+          <t>Comprehensive (income) loss                                            -                     -                       -           919,850    (2,272,847)       (1,352,997)Annual translation adjustment</t>
         </is>
       </c>
       <c r="D578" t="inlineStr"/>
@@ -60649,11 +60569,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H578" s="5" t="n">
-        <v>0.574226</v>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I578" s="5" t="n">
-        <v>-1.546224</v>
+        <v>0.02399</v>
       </c>
       <c r="J578" t="inlineStr">
         <is>
@@ -60712,14 +60634,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B579" t="inlineStr">
-        <is>
-          <t>(#)            $               $                 $                 ($)               ($)</t>
-        </is>
-      </c>
+      <c r="B579" t="inlineStr"/>
       <c r="C579" t="inlineStr">
         <is>
-          <t>- - - - (2,272,847) (2,272,847)Net loss and comprehensive loss for the period - - 919,850 919,850ComprehensiveCumulative translationloss adjustment 919,850</t>
+          <t>2015 $ March 31,</t>
         </is>
       </c>
       <c r="D579" t="inlineStr"/>
@@ -60739,10 +60657,10 @@
         </is>
       </c>
       <c r="H579" s="5" t="n">
-        <v>-1.352997</v>
+        <v>0.05315</v>
       </c>
       <c r="I579" s="5" t="n">
-        <v>-2.272847</v>
+        <v>0.002014</v>
       </c>
       <c r="J579" t="inlineStr">
         <is>
@@ -60803,12 +60721,12 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>(#)            $               $                 $                 ($)               ($)</t>
+          <t>328,193  Stock-based compensation                                                                             23,991</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>- - 23,990 - - 23,990 Stock based compensation 11,609,518 2,357,725 - - - 2,357,725 Shares issued for cash 266,010 71,190 - - - 71,190 Shares issued for agent and finders' fees 1,062,500 170,000 - - - 170,000 Shares issued for debt 6,827,442 2,730,977 - - - 2,730,977 Shares issued for investment in associate - (201,846) 95,349 - - (106,497) Share issuance costs 300,000 45,818 (15,818) - - 30,000Agent options exercised 35,000 10,500 - - - 10,500Warrants exercised - - 2,280,366 - - 2,280,366BalanceWarrants–issuedMarchfor31,investment2015 in associate 42,553,633 7,173,780 2,514,921 919,850</t>
+          <t>435,404 Share of loss in joint venture (note</t>
         </is>
       </c>
       <c r="D580" t="inlineStr"/>
@@ -60827,11 +60745,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H580" s="5" t="n">
-        <v>6.78948</v>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I580" s="5" t="n">
-        <v>-3.819071</v>
+        <v>1.1e-05</v>
       </c>
       <c r="J580" t="inlineStr">
         <is>
@@ -60892,12 +60812,12 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>(#)            $               $                 $                 ($)               ($)</t>
+          <t>328,193  Stock-based compensation                                                                             23,991</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Balance - March 31, 2013 12,493,163 890,243 107,043</t>
+          <t>(13,645) Write –down of exploration &amp; evaluation assets (note</t>
         </is>
       </c>
       <c r="D581" t="inlineStr"/>
@@ -60916,11 +60836,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H581" s="5" t="n">
-        <v>0.531843</v>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I581" s="5" t="n">
-        <v>-0.465443</v>
+        <v>1.2e-05</v>
       </c>
       <c r="J581" t="inlineStr">
         <is>
@@ -60981,12 +60903,12 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>(#)            $               $                 $                 ($)               ($)</t>
+          <t>Loss before income taxes                                                      (2,284,097)  Interest income                                                                                         (334)</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>(#)            $               $                 $                 ($)               ($) total</t>
+          <t>(note 13)</t>
         </is>
       </c>
       <c r="D582" t="inlineStr"/>
@@ -61006,10 +60928,10 @@
         </is>
       </c>
       <c r="H582" s="5" t="n">
-        <v>-1.080781</v>
+        <v>-1.105781</v>
       </c>
       <c r="I582" s="5" t="n">
-        <v>-1.080781</v>
+        <v>0.01125</v>
       </c>
       <c r="J582" t="inlineStr">
         <is>
@@ -61070,12 +60992,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>(#)            $               $                 $                 ($)               ($)</t>
+          <t>919,850</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>- (67,326) - - - (67,326) Shares issued in exchange for marketable securities Share issuance costs 450,000 83,000 - - - 83,000 Shares issued in connection with resource propertyBalanceacquisition– March 31, 2014 22,453,163 1,989,417 131,034</t>
+          <t>Comprehensive loss for the year (1,352,997) Cumulative translation adjustment</t>
         </is>
       </c>
       <c r="D583" t="inlineStr"/>
@@ -61095,10 +61017,12 @@
         </is>
       </c>
       <c r="H583" s="5" t="n">
-        <v>0.574226</v>
-      </c>
-      <c r="I583" s="5" t="n">
-        <v>-1.546224</v>
+        <v>-1.080781</v>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J583" t="inlineStr">
         <is>
@@ -61157,10 +61081,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B584" t="inlineStr"/>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>(#)            $               $                 $                 ($)               ($)</t>
+        </is>
+      </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>2014 $ March 31,</t>
+          <t>Balance - March 31, 2014 22,453,163 1,989,416 131,034 -</t>
         </is>
       </c>
       <c r="D584" t="inlineStr"/>
@@ -61174,16 +61102,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G584" s="5" t="n">
-        <v>0.593653</v>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H584" s="5" t="n">
-        <v>0.002013</v>
-      </c>
-      <c r="I584" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.574226</v>
+      </c>
+      <c r="I584" s="5" t="n">
+        <v>-1.546224</v>
       </c>
       <c r="J584" t="inlineStr">
         <is>
@@ -61244,12 +61172,12 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>23,991  Investor relations expense                                                                                                                               -</t>
+          <t>(#)            $               $                 $                 ($)               ($)</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Loss before other items (1,062,209) Stock-based compensation</t>
+          <t>- - - - (2,272,847) (2,272,847)Net loss and comprehensive loss for the period - - 919,850 919,850ComprehensiveCumulative translationloss adjustment 919,850</t>
         </is>
       </c>
       <c r="D585" t="inlineStr"/>
@@ -61263,16 +61191,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G585" s="5" t="n">
-        <v>-0.408493</v>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H585" s="5" t="n">
-        <v>0.091225</v>
-      </c>
-      <c r="I585" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.352997</v>
+      </c>
+      <c r="I585" s="5" t="n">
+        <v>-2.272847</v>
       </c>
       <c r="J585" t="inlineStr">
         <is>
@@ -61333,12 +61261,12 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Loss before income taxes                                                           (1,105,781)   Interest income                                                                                   29</t>
+          <t>(#)            $               $                 $                 ($)               ($)</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>(note 11) 25,000 (408,464)Net loss and comprehensive loss for the years attributable to shareholdersIncome tax recovery (1,080,781)</t>
+          <t>- - 23,990 - - 23,990 Stock based compensation 11,609,518 2,357,725 - - - 2,357,725 Shares issued for cash 266,010 71,190 - - - 71,190 Shares issued for agent and finders' fees 1,062,500 170,000 - - - 170,000 Shares issued for debt 6,827,442 2,730,977 - - - 2,730,977 Shares issued for investment in associate - (201,846) 95,349 - - (106,497) Share issuance costs 300,000 45,818 (15,818) - - 30,000Agent options exercised 35,000 10,500 - - - 10,500Warrants exercised - - 2,280,366 - - 2,280,366BalanceWarrants–issuedMarchfor31,investment2015 in associate 42,553,633 7,173,780 2,514,921 919,850</t>
         </is>
       </c>
       <c r="D586" t="inlineStr"/>
@@ -61352,16 +61280,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G586" s="5" t="n">
-        <v>-0.398464</v>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H586" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I586" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.78948</v>
+      </c>
+      <c r="I586" s="5" t="n">
+        <v>-3.819071</v>
       </c>
       <c r="J586" t="inlineStr">
         <is>
@@ -61422,12 +61350,12 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>(#)            $               $                 $                 ($)               ($)</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Balance – March 31, 2013 12,493,163 890,243 107,043</t>
+          <t>Balance - March 31, 2013 12,493,163 890,243 107,043</t>
         </is>
       </c>
       <c r="D587" t="inlineStr"/>
@@ -61441,16 +61369,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G587" s="5" t="n">
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H587" s="5" t="n">
         <v>0.531843</v>
       </c>
-      <c r="H587" s="5" t="n">
+      <c r="I587" s="5" t="n">
         <v>-0.465443</v>
-      </c>
-      <c r="I587" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="J587" t="inlineStr">
         <is>
@@ -61511,12 +61439,12 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>(#)            $               $                 $                 ($)               ($)</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>- - - (1,080,781) (1,080,781) Net loss and comprehensive loss for 4,910,000 245,500 - - 245,500 the year Shared issued for cash 4,200,000 798,000 - - 798,000 Shares issued for marketable 400,000 40,000 - - 40,000 securities Shares issued for debt 450,000 83,000 - - 83,000 Shares issued in connection with - (67,327) - - (67,327) resource property acquisition Share issuance costs - - 23,991 - 23,991 Stock-based compensation Balance – March 31, 2014 22,453,163 1,989,416 131,034</t>
+          <t>(#)            $               $                 $                 ($)               ($) total</t>
         </is>
       </c>
       <c r="D588" t="inlineStr"/>
@@ -61530,16 +61458,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G588" s="5" t="n">
-        <v>0.574226</v>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H588" s="5" t="n">
-        <v>-1.546224</v>
-      </c>
-      <c r="I588" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.080781</v>
+      </c>
+      <c r="I588" s="5" t="n">
+        <v>-1.080781</v>
       </c>
       <c r="J588" t="inlineStr">
         <is>
@@ -61600,12 +61528,12 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>(#)            $               $                 $                 ($)               ($)</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Balance – March 31, 2012 6,500,000 325,000 - (66,979) 258,021 Net loss and comprehensive loss for the year - - - (398,464) (398,464) Shared issued for cash 5,693,163 666,475 - - 666,475 Share issuance costs - (146,232) - - (146,232) Share-based compensation - - 91,225 - 91,225 Agent options - - 15,818 - 15,818 Shares issued in connection with resource property acquisition 300,000 45,000 - - 45,000 Balance –March 31, 2013 12,493,163 890,243 107,043</t>
+          <t>- (67,326) - - - (67,326) Shares issued in exchange for marketable securities Share issuance costs 450,000 83,000 - - - 83,000 Shares issued in connection with resource propertyBalanceacquisition– March 31, 2014 22,453,163 1,989,417 131,034</t>
         </is>
       </c>
       <c r="D589" t="inlineStr"/>
@@ -61619,16 +61547,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G589" s="5" t="n">
-        <v>0.531843</v>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H589" s="5" t="n">
-        <v>-0.465443</v>
-      </c>
-      <c r="I589" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.574226</v>
+      </c>
+      <c r="I589" s="5" t="n">
+        <v>-1.546224</v>
       </c>
       <c r="J589" t="inlineStr">
         <is>
@@ -61687,30 +61615,28 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B590" t="inlineStr">
-        <is>
-          <t>408,493  Stock-based compensation                                                                                                                                 -</t>
-        </is>
-      </c>
+      <c r="B590" t="inlineStr"/>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Loss before other items</t>
+          <t>2014 $ March 31,</t>
         </is>
       </c>
       <c r="D590" t="inlineStr"/>
-      <c r="E590" s="5" t="n">
-        <v>0.066979</v>
-      </c>
-      <c r="F590" s="5" t="n">
-        <v>-0.066979</v>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G590" s="5" t="n">
-        <v>-0.408493</v>
-      </c>
-      <c r="H590" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.593653</v>
+      </c>
+      <c r="H590" s="5" t="n">
+        <v>0.002013</v>
       </c>
       <c r="I590" t="inlineStr">
         <is>
@@ -61776,12 +61702,12 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>29Other items</t>
+          <t>23,991  Investor relations expense                                                                                                                               -</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>10,000 Interest income -Net loss and comprehensive loss for the period attributable toshareholdersFuture income tax expense</t>
+          <t>Loss before other items (1,062,209) Stock-based compensation</t>
         </is>
       </c>
       <c r="D591" t="inlineStr"/>
@@ -61790,16 +61716,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F591" s="5" t="n">
-        <v>-0.066979</v>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G591" s="5" t="n">
-        <v>-0.398464</v>
-      </c>
-      <c r="H591" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.408493</v>
+      </c>
+      <c r="H591" s="5" t="n">
+        <v>0.091225</v>
       </c>
       <c r="I591" t="inlineStr">
         <is>
@@ -61865,30 +61791,30 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>($)</t>
+          <t>Loss before income taxes                                                           (1,105,781)   Interest income                                                                                   29</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Balance – March 31, 2012 6,500,000 325,000</t>
+          <t>(note 11) 25,000 (408,464)Net loss and comprehensive loss for the years attributable to shareholdersIncome tax recovery (1,080,781)</t>
         </is>
       </c>
       <c r="D592" t="inlineStr"/>
-      <c r="E592" s="5" t="n">
-        <v>-0.066979</v>
-      </c>
-      <c r="F592" s="5" t="n">
-        <v>0.258021</v>
-      </c>
-      <c r="G592" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H592" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G592" s="5" t="n">
+        <v>-0.398464</v>
+      </c>
+      <c r="H592" s="5" t="n">
+        <v>0.01</v>
       </c>
       <c r="I592" t="inlineStr">
         <is>
@@ -61954,12 +61880,12 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>($)</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>- - - (398,464) (398,464) Net loss and comprehensive loss for 5,693,163 666,475 - - 666,475 the period Shared issued for cash - (146,232) - - (146,232) Share issuance costs - -</t>
+          <t>Balance – March 31, 2013 12,493,163 890,243 107,043</t>
         </is>
       </c>
       <c r="D593" t="inlineStr"/>
@@ -61968,16 +61894,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F593" s="5" t="n">
-        <v>0.091225</v>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G593" s="5" t="n">
-        <v>0.091225</v>
-      </c>
-      <c r="H593" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.531843</v>
+      </c>
+      <c r="H593" s="5" t="n">
+        <v>-0.465443</v>
       </c>
       <c r="I593" t="inlineStr">
         <is>
@@ -62043,28 +61969,30 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>($)</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>300,000 45,000 - - 45,000 Shares issued in connection withBalanceresource– Marchproperty31, 2013acquisition 12,493,163 890,243</t>
+          <t>- - - (1,080,781) (1,080,781) Net loss and comprehensive loss for 4,910,000 245,500 - - 245,500 the year Shared issued for cash 4,200,000 798,000 - - 798,000 Shares issued for marketable 400,000 40,000 - - 40,000 securities Shares issued for debt 450,000 83,000 - - 83,000 Shares issued in connection with - (67,327) - - (67,327) resource property acquisition Share issuance costs - - 23,991 - 23,991 Stock-based compensation Balance – March 31, 2014 22,453,163 1,989,416 131,034</t>
         </is>
       </c>
       <c r="D594" t="inlineStr"/>
-      <c r="E594" s="5" t="n">
-        <v>-0.465443</v>
-      </c>
-      <c r="F594" s="5" t="n">
-        <v>0.531843</v>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G594" s="5" t="n">
-        <v>0.107043</v>
-      </c>
-      <c r="H594" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.574226</v>
+      </c>
+      <c r="H594" s="5" t="n">
+        <v>-1.546224</v>
       </c>
       <c r="I594" t="inlineStr">
         <is>
@@ -62130,82 +62058,1079 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Balance – March 31, 2012 6,500,000 325,000 - (66,979) 258,021 Net loss and comprehensive loss for the year - - - (398,464) (398,464) Shared issued for cash 5,693,163 666,475 - - 666,475 Share issuance costs - (146,232) - - (146,232) Share-based compensation - - 91,225 - 91,225 Agent options - - 15,818 - 15,818 Shares issued in connection with resource property acquisition 300,000 45,000 - - 45,000 Balance –March 31, 2013 12,493,163 890,243 107,043</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr"/>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G595" s="5" t="n">
+        <v>0.531843</v>
+      </c>
+      <c r="H595" s="5" t="n">
+        <v>-0.465443</v>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M595" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N595" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O595" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P595" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q595" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R595" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S595" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>408,493  Stock-based compensation                                                                                                                                 -</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Loss before other items</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr"/>
+      <c r="E596" s="5" t="n">
+        <v>0.066979</v>
+      </c>
+      <c r="F596" s="5" t="n">
+        <v>-0.066979</v>
+      </c>
+      <c r="G596" s="5" t="n">
+        <v>-0.408493</v>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M596" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N596" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O596" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P596" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q596" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R596" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S596" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>29Other items</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>10,000 Interest income -Net loss and comprehensive loss for the period attributable toshareholdersFuture income tax expense</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr"/>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F597" s="5" t="n">
+        <v>-0.066979</v>
+      </c>
+      <c r="G597" s="5" t="n">
+        <v>-0.398464</v>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N597" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O597" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P597" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q597" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R597" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S597" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
           <t>($)</t>
         </is>
       </c>
-      <c r="C595" t="inlineStr">
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Balance – March 31, 2012 6,500,000 325,000</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr"/>
+      <c r="E598" s="5" t="n">
+        <v>-0.066979</v>
+      </c>
+      <c r="F598" s="5" t="n">
+        <v>0.258021</v>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M598" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N598" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O598" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P598" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q598" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R598" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S598" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>($)</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>- - - (398,464) (398,464) Net loss and comprehensive loss for 5,693,163 666,475 - - 666,475 the period Shared issued for cash - (146,232) - - (146,232) Share issuance costs - -</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr"/>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F599" s="5" t="n">
+        <v>0.091225</v>
+      </c>
+      <c r="G599" s="5" t="n">
+        <v>0.091225</v>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N599" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O599" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P599" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q599" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R599" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S599" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>($)</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>300,000 45,000 - - 45,000 Shares issued in connection withBalanceresource– Marchproperty31, 2013acquisition 12,493,163 890,243</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr"/>
+      <c r="E600" s="5" t="n">
+        <v>-0.465443</v>
+      </c>
+      <c r="F600" s="5" t="n">
+        <v>0.531843</v>
+      </c>
+      <c r="G600" s="5" t="n">
+        <v>0.107043</v>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M600" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N600" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O600" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P600" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q600" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R600" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S600" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>($)</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
         <is>
           <t>Balance – June 6, 2011 - - - - - Net loss and comprehensive loss for the period - - - (66,979) (66,979) SharesBalanceissued–Marchfor 31,cash2012 6,500,000 325,000 - - 325,000 6,500,000 325,000</t>
         </is>
       </c>
-      <c r="D595" t="inlineStr"/>
-      <c r="E595" s="5" t="n">
+      <c r="D601" t="inlineStr"/>
+      <c r="E601" s="5" t="n">
         <v>-0.066979</v>
       </c>
-      <c r="F595" s="5" t="n">
+      <c r="F601" s="5" t="n">
         <v>0.258021</v>
       </c>
-      <c r="G595" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H595" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I595" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J595" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K595" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L595" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M595" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N595" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O595" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P595" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q595" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R595" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S595" t="inlineStr">
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M601" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N601" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O601" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P601" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q601" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R601" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S601" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F602" s="5" t="n">
+        <v>0.047997</v>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N602" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O602" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P602" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q602" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R602" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S602" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Transfer, filing and listing fees</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr"/>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F603" s="5" t="n">
+        <v>0.018982</v>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the period attributable to shareholders</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr"/>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F604" s="5" t="n">
+        <v>0.066979</v>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Loss per share</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F605" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F606" s="5" t="n">
+        <v>-1.831104</v>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S606" t="inlineStr">
         <is>
           <t>-</t>
         </is>
